--- a/data/flat/soccer.xlsx
+++ b/data/flat/soccer.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ82" headerRowCount="1">
-  <autoFilter ref="A1:CQ82"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR83" headerRowCount="1">
+  <autoFilter ref="A1:CR83"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$82)</f>
+        <f>COUNTA('Picks'!$A$2:$A$83)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$82,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$83,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$82,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$83,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"win")+COUNTIFS('Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"win")+COUNTIFS('Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$82,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$83,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"win")/(COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"win")+COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"win")/(COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"win")+COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$82)/SUM('Picks'!$BX$2:$BX$82),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$83)/SUM('Picks'!$BX$2:$BX$83),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$82)</f>
+        <f>SUM('Picks'!$BY$2:$BY$83)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$82,"&lt;&gt;",'Picks'!$AB$2:$AB$82),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$83,"&lt;&gt;",'Picks'!$AB$2:$AB$83),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$82,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$82,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$83,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$83,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$82,'Picks'!$AM$2:$AM$82,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$83,'Picks'!$AM$2:$AM$83,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$82,$A14,'Picks'!$U$2:$U$82,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$83,$A14,'Picks'!$U$2:$U$83,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$82,$A14,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$83,$A14,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$82,$A14,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$83,$A14,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$82,'Picks'!$H$2:$H$82,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$83,'Picks'!$H$2:$H$83,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$82,'Picks'!$H$2:$H$82,$A14,'Picks'!$U$2:$U$82,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$83,'Picks'!$H$2:$H$83,$A14,'Picks'!$U$2:$U$83,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$82,$A15,'Picks'!$U$2:$U$82,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$83,$A15,'Picks'!$U$2:$U$83,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$82,$A15,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$83,$A15,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$82,$A15,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$83,$A15,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$82,'Picks'!$H$2:$H$82,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$83,'Picks'!$H$2:$H$83,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$82,'Picks'!$H$2:$H$82,$A15,'Picks'!$U$2:$U$82,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$83,'Picks'!$H$2:$H$83,$A15,'Picks'!$U$2:$U$83,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$82,$A16,'Picks'!$U$2:$U$82,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$83,$A16,'Picks'!$U$2:$U$83,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$82,$A16,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$83,$A16,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$82,$A16,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$83,$A16,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$82,'Picks'!$H$2:$H$82,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$83,'Picks'!$H$2:$H$83,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$82,'Picks'!$H$2:$H$82,$A16,'Picks'!$U$2:$U$82,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$83,'Picks'!$H$2:$H$83,$A16,'Picks'!$U$2:$U$83,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ82"/>
+  <dimension ref="A1:CR83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1871,6 +1878,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2150,6 +2158,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2433,6 +2442,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2712,6 +2722,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2991,6 +3002,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3270,6 +3282,7 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3549,6 +3562,7 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3828,6 +3842,7 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4107,6 +4122,7 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4386,6 +4402,7 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4665,6 +4682,7 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4944,6 +4962,7 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5223,6 +5242,7 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5502,6 +5522,7 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5781,6 +5802,7 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6060,6 +6082,7 @@
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6339,6 +6362,7 @@
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6618,6 +6642,7 @@
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -6897,6 +6922,7 @@
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7176,6 +7202,7 @@
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7455,6 +7482,7 @@
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7734,6 +7762,7 @@
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -8013,6 +8042,7 @@
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8292,6 +8322,7 @@
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8571,6 +8602,7 @@
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -8850,6 +8882,7 @@
       <c r="CO27" s="24" t="n"/>
       <c r="CP27" s="24" t="n"/>
       <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9133,6 +9166,7 @@
       <c r="CO28" s="24" t="n"/>
       <c r="CP28" s="24" t="n"/>
       <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9416,6 +9450,7 @@
       <c r="CO29" s="24" t="n"/>
       <c r="CP29" s="24" t="n"/>
       <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9699,6 +9734,7 @@
       <c r="CO30" s="24" t="n"/>
       <c r="CP30" s="24" t="n"/>
       <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -9982,6 +10018,7 @@
       <c r="CO31" s="24" t="n"/>
       <c r="CP31" s="24" t="n"/>
       <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10261,6 +10298,7 @@
       <c r="CO32" s="24" t="n"/>
       <c r="CP32" s="24" t="n"/>
       <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -10540,6 +10578,7 @@
       <c r="CO33" s="24" t="n"/>
       <c r="CP33" s="24" t="n"/>
       <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -10819,6 +10858,7 @@
       <c r="CO34" s="24" t="n"/>
       <c r="CP34" s="24" t="n"/>
       <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -11098,6 +11138,7 @@
       <c r="CO35" s="24" t="n"/>
       <c r="CP35" s="24" t="n"/>
       <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -11377,6 +11418,7 @@
       <c r="CO36" s="24" t="n"/>
       <c r="CP36" s="24" t="n"/>
       <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -11660,6 +11702,7 @@
       <c r="CO37" s="24" t="n"/>
       <c r="CP37" s="24" t="n"/>
       <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
@@ -11943,6 +11986,7 @@
       <c r="CO38" s="24" t="n"/>
       <c r="CP38" s="24" t="n"/>
       <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
@@ -12226,6 +12270,7 @@
       <c r="CO39" s="24" t="n"/>
       <c r="CP39" s="24" t="n"/>
       <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
@@ -12509,6 +12554,7 @@
       <c r="CO40" s="24" t="n"/>
       <c r="CP40" s="24" t="n"/>
       <c r="CQ40" s="24" t="n"/>
+      <c r="CR40" s="24" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
@@ -12792,6 +12838,7 @@
       <c r="CO41" s="24" t="n"/>
       <c r="CP41" s="24" t="n"/>
       <c r="CQ41" s="24" t="n"/>
+      <c r="CR41" s="24" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
@@ -13075,6 +13122,7 @@
       <c r="CO42" s="24" t="n"/>
       <c r="CP42" s="24" t="n"/>
       <c r="CQ42" s="24" t="n"/>
+      <c r="CR42" s="24" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
@@ -13358,6 +13406,7 @@
       <c r="CO43" s="24" t="n"/>
       <c r="CP43" s="24" t="n"/>
       <c r="CQ43" s="24" t="n"/>
+      <c r="CR43" s="24" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
@@ -13637,6 +13686,7 @@
       <c r="CO44" s="24" t="n"/>
       <c r="CP44" s="24" t="n"/>
       <c r="CQ44" s="24" t="n"/>
+      <c r="CR44" s="24" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
@@ -13916,6 +13966,7 @@
       <c r="CO45" s="24" t="n"/>
       <c r="CP45" s="24" t="n"/>
       <c r="CQ45" s="24" t="n"/>
+      <c r="CR45" s="24" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
@@ -14195,6 +14246,7 @@
       <c r="CO46" s="24" t="n"/>
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="n"/>
+      <c r="CR46" s="24" t="n"/>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
@@ -14474,6 +14526,7 @@
       <c r="CO47" s="24" t="n"/>
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="n"/>
+      <c r="CR47" s="24" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
@@ -14753,6 +14806,7 @@
       <c r="CO48" s="24" t="n"/>
       <c r="CP48" s="24" t="n"/>
       <c r="CQ48" s="24" t="n"/>
+      <c r="CR48" s="24" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
@@ -15032,6 +15086,7 @@
       <c r="CO49" s="24" t="n"/>
       <c r="CP49" s="24" t="n"/>
       <c r="CQ49" s="24" t="n"/>
+      <c r="CR49" s="24" t="n"/>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
@@ -15311,6 +15366,7 @@
       <c r="CO50" s="24" t="n"/>
       <c r="CP50" s="24" t="n"/>
       <c r="CQ50" s="24" t="n"/>
+      <c r="CR50" s="24" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
@@ -15590,6 +15646,7 @@
       <c r="CO51" s="24" t="n"/>
       <c r="CP51" s="24" t="n"/>
       <c r="CQ51" s="24" t="n"/>
+      <c r="CR51" s="24" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
@@ -15869,6 +15926,7 @@
       <c r="CO52" s="24" t="n"/>
       <c r="CP52" s="24" t="n"/>
       <c r="CQ52" s="24" t="n"/>
+      <c r="CR52" s="24" t="n"/>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
@@ -16147,7 +16205,8 @@
       <c r="CN53" s="24" t="n"/>
       <c r="CO53" s="24" t="n"/>
       <c r="CP53" s="24" t="n"/>
-      <c r="CQ53" s="24" t="inlineStr">
+      <c r="CQ53" s="24" t="n"/>
+      <c r="CR53" s="24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -16431,6 +16490,7 @@
       <c r="CO54" s="24" t="n"/>
       <c r="CP54" s="24" t="n"/>
       <c r="CQ54" s="24" t="n"/>
+      <c r="CR54" s="24" t="n"/>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
@@ -16710,6 +16770,7 @@
       <c r="CO55" s="24" t="n"/>
       <c r="CP55" s="24" t="n"/>
       <c r="CQ55" s="24" t="n"/>
+      <c r="CR55" s="24" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
@@ -16989,6 +17050,7 @@
       <c r="CO56" s="24" t="n"/>
       <c r="CP56" s="24" t="n"/>
       <c r="CQ56" s="24" t="n"/>
+      <c r="CR56" s="24" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
@@ -17268,6 +17330,7 @@
       <c r="CO57" s="24" t="n"/>
       <c r="CP57" s="24" t="n"/>
       <c r="CQ57" s="24" t="n"/>
+      <c r="CR57" s="24" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
@@ -17547,6 +17610,7 @@
       <c r="CO58" s="24" t="n"/>
       <c r="CP58" s="24" t="n"/>
       <c r="CQ58" s="24" t="n"/>
+      <c r="CR58" s="24" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
@@ -17826,6 +17890,7 @@
       <c r="CO59" s="24" t="n"/>
       <c r="CP59" s="24" t="n"/>
       <c r="CQ59" s="24" t="n"/>
+      <c r="CR59" s="24" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
@@ -18105,6 +18170,7 @@
       <c r="CO60" s="24" t="n"/>
       <c r="CP60" s="24" t="n"/>
       <c r="CQ60" s="24" t="n"/>
+      <c r="CR60" s="24" t="n"/>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
@@ -18384,6 +18450,7 @@
       <c r="CO61" s="24" t="n"/>
       <c r="CP61" s="24" t="n"/>
       <c r="CQ61" s="24" t="n"/>
+      <c r="CR61" s="24" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
@@ -18663,6 +18730,7 @@
       <c r="CO62" s="24" t="n"/>
       <c r="CP62" s="24" t="n"/>
       <c r="CQ62" s="24" t="n"/>
+      <c r="CR62" s="24" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
@@ -18942,6 +19010,7 @@
       <c r="CO63" s="24" t="n"/>
       <c r="CP63" s="24" t="n"/>
       <c r="CQ63" s="24" t="n"/>
+      <c r="CR63" s="24" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
@@ -19221,6 +19290,7 @@
       <c r="CO64" s="24" t="n"/>
       <c r="CP64" s="24" t="n"/>
       <c r="CQ64" s="24" t="n"/>
+      <c r="CR64" s="24" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
@@ -19500,6 +19570,7 @@
       <c r="CO65" s="24" t="n"/>
       <c r="CP65" s="24" t="n"/>
       <c r="CQ65" s="24" t="n"/>
+      <c r="CR65" s="24" t="n"/>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
@@ -19779,6 +19850,7 @@
       <c r="CO66" s="24" t="n"/>
       <c r="CP66" s="24" t="n"/>
       <c r="CQ66" s="24" t="n"/>
+      <c r="CR66" s="24" t="n"/>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
@@ -20058,6 +20130,7 @@
       <c r="CO67" s="24" t="n"/>
       <c r="CP67" s="24" t="n"/>
       <c r="CQ67" s="24" t="n"/>
+      <c r="CR67" s="24" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
@@ -20337,6 +20410,7 @@
       <c r="CO68" s="24" t="n"/>
       <c r="CP68" s="24" t="n"/>
       <c r="CQ68" s="24" t="n"/>
+      <c r="CR68" s="24" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
@@ -20615,7 +20689,8 @@
       <c r="CN69" s="24" t="n"/>
       <c r="CO69" s="24" t="n"/>
       <c r="CP69" s="24" t="n"/>
-      <c r="CQ69" s="24" t="inlineStr">
+      <c r="CQ69" s="24" t="n"/>
+      <c r="CR69" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -20898,7 +20973,8 @@
       <c r="CN70" s="24" t="n"/>
       <c r="CO70" s="24" t="n"/>
       <c r="CP70" s="24" t="n"/>
-      <c r="CQ70" s="24" t="inlineStr">
+      <c r="CQ70" s="24" t="n"/>
+      <c r="CR70" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -21181,7 +21257,8 @@
       <c r="CN71" s="24" t="n"/>
       <c r="CO71" s="24" t="n"/>
       <c r="CP71" s="24" t="n"/>
-      <c r="CQ71" s="24" t="inlineStr">
+      <c r="CQ71" s="24" t="n"/>
+      <c r="CR71" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -21464,7 +21541,8 @@
       <c r="CN72" s="24" t="n"/>
       <c r="CO72" s="24" t="n"/>
       <c r="CP72" s="24" t="n"/>
-      <c r="CQ72" s="24" t="inlineStr">
+      <c r="CQ72" s="24" t="n"/>
+      <c r="CR72" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -21747,7 +21825,8 @@
       <c r="CN73" s="24" t="n"/>
       <c r="CO73" s="24" t="n"/>
       <c r="CP73" s="24" t="n"/>
-      <c r="CQ73" s="24" t="inlineStr">
+      <c r="CQ73" s="24" t="n"/>
+      <c r="CR73" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -22030,7 +22109,8 @@
       <c r="CN74" s="24" t="n"/>
       <c r="CO74" s="24" t="n"/>
       <c r="CP74" s="24" t="n"/>
-      <c r="CQ74" s="24" t="inlineStr">
+      <c r="CQ74" s="24" t="n"/>
+      <c r="CR74" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -22313,7 +22393,8 @@
       <c r="CN75" s="24" t="n"/>
       <c r="CO75" s="24" t="n"/>
       <c r="CP75" s="24" t="n"/>
-      <c r="CQ75" s="24" t="inlineStr">
+      <c r="CQ75" s="24" t="n"/>
+      <c r="CR75" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -22596,7 +22677,8 @@
       <c r="CN76" s="24" t="n"/>
       <c r="CO76" s="24" t="n"/>
       <c r="CP76" s="24" t="n"/>
-      <c r="CQ76" s="24" t="inlineStr">
+      <c r="CQ76" s="24" t="n"/>
+      <c r="CR76" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -22879,7 +22961,8 @@
       <c r="CN77" s="24" t="n"/>
       <c r="CO77" s="24" t="n"/>
       <c r="CP77" s="24" t="n"/>
-      <c r="CQ77" s="24" t="inlineStr">
+      <c r="CQ77" s="24" t="n"/>
+      <c r="CR77" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -23162,7 +23245,8 @@
       <c r="CN78" s="24" t="n"/>
       <c r="CO78" s="24" t="n"/>
       <c r="CP78" s="24" t="n"/>
-      <c r="CQ78" s="24" t="inlineStr">
+      <c r="CQ78" s="24" t="n"/>
+      <c r="CR78" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -23445,7 +23529,8 @@
       <c r="CN79" s="24" t="n"/>
       <c r="CO79" s="24" t="n"/>
       <c r="CP79" s="24" t="n"/>
-      <c r="CQ79" s="24" t="inlineStr">
+      <c r="CQ79" s="24" t="n"/>
+      <c r="CR79" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -23728,7 +23813,8 @@
       <c r="CN80" s="24" t="n"/>
       <c r="CO80" s="24" t="n"/>
       <c r="CP80" s="24" t="n"/>
-      <c r="CQ80" s="24" t="inlineStr">
+      <c r="CQ80" s="24" t="n"/>
+      <c r="CR80" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -24011,7 +24097,8 @@
       <c r="CN81" s="24" t="n"/>
       <c r="CO81" s="24" t="n"/>
       <c r="CP81" s="24" t="n"/>
-      <c r="CQ81" s="24" t="inlineStr">
+      <c r="CQ81" s="24" t="n"/>
+      <c r="CR81" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -24294,7 +24381,278 @@
       <c r="CN82" s="24" t="n"/>
       <c r="CO82" s="24" t="n"/>
       <c r="CP82" s="24" t="n"/>
-      <c r="CQ82" s="24" t="inlineStr">
+      <c r="CQ82" s="24" t="n"/>
+      <c r="CR82" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>6b9b9246d1ba456a</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:31.878300Z</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>401886532</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J83" s="25" t="n"/>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L83" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="M83" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="N83" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="O83" s="28" t="n">
+        <v>0.480757</v>
+      </c>
+      <c r="P83" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q83" s="28" t="n">
+        <v>-0.399195</v>
+      </c>
+      <c r="R83" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U83" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V83" s="24" t="n"/>
+      <c r="W83" s="26" t="n"/>
+      <c r="X83" s="26" t="n"/>
+      <c r="Y83" s="25" t="n"/>
+      <c r="Z83" s="26" t="n"/>
+      <c r="AA83" s="28" t="n"/>
+      <c r="AB83" s="28" t="n"/>
+      <c r="AC83" s="30" t="n"/>
+      <c r="AD83" s="24" t="n"/>
+      <c r="AE83" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.07 (home) / 1.59 (away) from EWMA attack/defense strengths. Executable ask 0.8800 (atc-clbf-nc-ars-2026-08-04-ars).</t>
+        </is>
+      </c>
+      <c r="AF83" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG83" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH83" s="24" t="n"/>
+      <c r="AI83" s="31" t="n"/>
+      <c r="AJ83" s="31" t="n"/>
+      <c r="AK83" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL83" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM83" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN83" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO83" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP83" s="24" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="AQ83" s="24" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="AR83" s="24" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="AS83" s="24" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="AT83" s="24" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="AU83" s="24" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="AV83" s="24" t="n"/>
+      <c r="AW83" s="24" t="n"/>
+      <c r="AX83" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY83" s="24" t="n"/>
+      <c r="AZ83" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA83" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB83" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC83" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD83" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE83" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF83" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG83" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH83" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.570932Z</t>
+        </is>
+      </c>
+      <c r="BI83" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ83" s="25" t="n"/>
+      <c r="BK83" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="BL83" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="BM83" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="BN83" s="28" t="n"/>
+      <c r="BO83" s="28" t="n"/>
+      <c r="BP83" s="25" t="n"/>
+      <c r="BQ83" s="27" t="n"/>
+      <c r="BR83" s="28" t="n"/>
+      <c r="BS83" s="28" t="n"/>
+      <c r="BT83" s="28" t="n"/>
+      <c r="BU83" s="25" t="n"/>
+      <c r="BV83" s="29" t="n"/>
+      <c r="BW83" s="24" t="n"/>
+      <c r="BX83" s="30" t="n"/>
+      <c r="BY83" s="27" t="n"/>
+      <c r="BZ83" s="24" t="n"/>
+      <c r="CA83" s="31" t="n"/>
+      <c r="CB83" s="24" t="n"/>
+      <c r="CC83" s="24" t="n"/>
+      <c r="CD83" s="24" t="n"/>
+      <c r="CE83" s="24" t="n"/>
+      <c r="CF83" s="24" t="n"/>
+      <c r="CG83" s="24" t="n"/>
+      <c r="CH83" s="24" t="n"/>
+      <c r="CI83" s="24" t="n"/>
+      <c r="CJ83" s="24" t="n"/>
+      <c r="CK83" s="24" t="n"/>
+      <c r="CL83" s="24" t="n"/>
+      <c r="CM83" s="24" t="n"/>
+      <c r="CN83" s="24" t="n"/>
+      <c r="CO83" s="24" t="n"/>
+      <c r="CP83" s="24" t="n"/>
+      <c r="CQ83" s="24" t="n"/>
+      <c r="CR83" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/flat/soccer.xlsx
+++ b/data/flat/soccer.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR83" headerRowCount="1">
-  <autoFilter ref="A1:CR83"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS83" headerRowCount="1">
+  <autoFilter ref="A1:CS83"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR83"/>
+  <dimension ref="A1:CS83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1879,6 +1886,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2159,6 +2167,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2443,6 +2452,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2723,6 +2733,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3003,6 +3014,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3283,6 +3295,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3563,6 +3576,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3843,6 +3857,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4123,6 +4138,7 @@
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
       <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4403,6 +4419,7 @@
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
       <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4683,6 +4700,7 @@
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
       <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4963,6 +4981,7 @@
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
       <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5243,6 +5262,7 @@
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
       <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5523,6 +5543,7 @@
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
       <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5803,6 +5824,7 @@
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
       <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6083,6 +6105,7 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
       <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6363,6 +6386,7 @@
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
       <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6643,6 +6667,7 @@
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
       <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -6923,6 +6948,7 @@
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
       <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7203,6 +7229,7 @@
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
       <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7483,6 +7510,7 @@
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
       <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7763,6 +7791,7 @@
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
       <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -8043,6 +8072,7 @@
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
       <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8323,6 +8353,7 @@
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
       <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8603,6 +8634,7 @@
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="n"/>
       <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -8883,6 +8915,7 @@
       <c r="CP27" s="24" t="n"/>
       <c r="CQ27" s="24" t="n"/>
       <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9167,6 +9200,7 @@
       <c r="CP28" s="24" t="n"/>
       <c r="CQ28" s="24" t="n"/>
       <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9451,6 +9485,7 @@
       <c r="CP29" s="24" t="n"/>
       <c r="CQ29" s="24" t="n"/>
       <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9735,6 +9770,7 @@
       <c r="CP30" s="24" t="n"/>
       <c r="CQ30" s="24" t="n"/>
       <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -10019,6 +10055,7 @@
       <c r="CP31" s="24" t="n"/>
       <c r="CQ31" s="24" t="n"/>
       <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10299,6 +10336,7 @@
       <c r="CP32" s="24" t="n"/>
       <c r="CQ32" s="24" t="n"/>
       <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -10579,6 +10617,7 @@
       <c r="CP33" s="24" t="n"/>
       <c r="CQ33" s="24" t="n"/>
       <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -10859,6 +10898,7 @@
       <c r="CP34" s="24" t="n"/>
       <c r="CQ34" s="24" t="n"/>
       <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -11139,6 +11179,7 @@
       <c r="CP35" s="24" t="n"/>
       <c r="CQ35" s="24" t="n"/>
       <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -11419,6 +11460,7 @@
       <c r="CP36" s="24" t="n"/>
       <c r="CQ36" s="24" t="n"/>
       <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -11703,6 +11745,7 @@
       <c r="CP37" s="24" t="n"/>
       <c r="CQ37" s="24" t="n"/>
       <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
@@ -11987,6 +12030,7 @@
       <c r="CP38" s="24" t="n"/>
       <c r="CQ38" s="24" t="n"/>
       <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
@@ -12271,6 +12315,7 @@
       <c r="CP39" s="24" t="n"/>
       <c r="CQ39" s="24" t="n"/>
       <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
@@ -12555,6 +12600,7 @@
       <c r="CP40" s="24" t="n"/>
       <c r="CQ40" s="24" t="n"/>
       <c r="CR40" s="24" t="n"/>
+      <c r="CS40" s="24" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
@@ -12839,6 +12885,7 @@
       <c r="CP41" s="24" t="n"/>
       <c r="CQ41" s="24" t="n"/>
       <c r="CR41" s="24" t="n"/>
+      <c r="CS41" s="24" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
@@ -13123,6 +13170,7 @@
       <c r="CP42" s="24" t="n"/>
       <c r="CQ42" s="24" t="n"/>
       <c r="CR42" s="24" t="n"/>
+      <c r="CS42" s="24" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
@@ -13407,6 +13455,7 @@
       <c r="CP43" s="24" t="n"/>
       <c r="CQ43" s="24" t="n"/>
       <c r="CR43" s="24" t="n"/>
+      <c r="CS43" s="24" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
@@ -13687,6 +13736,7 @@
       <c r="CP44" s="24" t="n"/>
       <c r="CQ44" s="24" t="n"/>
       <c r="CR44" s="24" t="n"/>
+      <c r="CS44" s="24" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
@@ -13967,6 +14017,7 @@
       <c r="CP45" s="24" t="n"/>
       <c r="CQ45" s="24" t="n"/>
       <c r="CR45" s="24" t="n"/>
+      <c r="CS45" s="24" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
@@ -14247,6 +14298,7 @@
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="n"/>
       <c r="CR46" s="24" t="n"/>
+      <c r="CS46" s="24" t="n"/>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
@@ -14527,6 +14579,7 @@
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="n"/>
       <c r="CR47" s="24" t="n"/>
+      <c r="CS47" s="24" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
@@ -14807,6 +14860,7 @@
       <c r="CP48" s="24" t="n"/>
       <c r="CQ48" s="24" t="n"/>
       <c r="CR48" s="24" t="n"/>
+      <c r="CS48" s="24" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
@@ -15087,6 +15141,7 @@
       <c r="CP49" s="24" t="n"/>
       <c r="CQ49" s="24" t="n"/>
       <c r="CR49" s="24" t="n"/>
+      <c r="CS49" s="24" t="n"/>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
@@ -15367,6 +15422,7 @@
       <c r="CP50" s="24" t="n"/>
       <c r="CQ50" s="24" t="n"/>
       <c r="CR50" s="24" t="n"/>
+      <c r="CS50" s="24" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
@@ -15647,6 +15703,7 @@
       <c r="CP51" s="24" t="n"/>
       <c r="CQ51" s="24" t="n"/>
       <c r="CR51" s="24" t="n"/>
+      <c r="CS51" s="24" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
@@ -15927,6 +15984,7 @@
       <c r="CP52" s="24" t="n"/>
       <c r="CQ52" s="24" t="n"/>
       <c r="CR52" s="24" t="n"/>
+      <c r="CS52" s="24" t="n"/>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
@@ -16206,7 +16264,8 @@
       <c r="CO53" s="24" t="n"/>
       <c r="CP53" s="24" t="n"/>
       <c r="CQ53" s="24" t="n"/>
-      <c r="CR53" s="24" t="inlineStr">
+      <c r="CR53" s="24" t="n"/>
+      <c r="CS53" s="24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -16491,6 +16550,7 @@
       <c r="CP54" s="24" t="n"/>
       <c r="CQ54" s="24" t="n"/>
       <c r="CR54" s="24" t="n"/>
+      <c r="CS54" s="24" t="n"/>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
@@ -16771,6 +16831,7 @@
       <c r="CP55" s="24" t="n"/>
       <c r="CQ55" s="24" t="n"/>
       <c r="CR55" s="24" t="n"/>
+      <c r="CS55" s="24" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
@@ -17051,6 +17112,7 @@
       <c r="CP56" s="24" t="n"/>
       <c r="CQ56" s="24" t="n"/>
       <c r="CR56" s="24" t="n"/>
+      <c r="CS56" s="24" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
@@ -17331,6 +17393,7 @@
       <c r="CP57" s="24" t="n"/>
       <c r="CQ57" s="24" t="n"/>
       <c r="CR57" s="24" t="n"/>
+      <c r="CS57" s="24" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
@@ -17611,6 +17674,7 @@
       <c r="CP58" s="24" t="n"/>
       <c r="CQ58" s="24" t="n"/>
       <c r="CR58" s="24" t="n"/>
+      <c r="CS58" s="24" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
@@ -17891,6 +17955,7 @@
       <c r="CP59" s="24" t="n"/>
       <c r="CQ59" s="24" t="n"/>
       <c r="CR59" s="24" t="n"/>
+      <c r="CS59" s="24" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
@@ -18171,6 +18236,7 @@
       <c r="CP60" s="24" t="n"/>
       <c r="CQ60" s="24" t="n"/>
       <c r="CR60" s="24" t="n"/>
+      <c r="CS60" s="24" t="n"/>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
@@ -18451,6 +18517,7 @@
       <c r="CP61" s="24" t="n"/>
       <c r="CQ61" s="24" t="n"/>
       <c r="CR61" s="24" t="n"/>
+      <c r="CS61" s="24" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
@@ -18731,6 +18798,7 @@
       <c r="CP62" s="24" t="n"/>
       <c r="CQ62" s="24" t="n"/>
       <c r="CR62" s="24" t="n"/>
+      <c r="CS62" s="24" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
@@ -19011,6 +19079,7 @@
       <c r="CP63" s="24" t="n"/>
       <c r="CQ63" s="24" t="n"/>
       <c r="CR63" s="24" t="n"/>
+      <c r="CS63" s="24" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
@@ -19291,6 +19360,7 @@
       <c r="CP64" s="24" t="n"/>
       <c r="CQ64" s="24" t="n"/>
       <c r="CR64" s="24" t="n"/>
+      <c r="CS64" s="24" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
@@ -19571,6 +19641,7 @@
       <c r="CP65" s="24" t="n"/>
       <c r="CQ65" s="24" t="n"/>
       <c r="CR65" s="24" t="n"/>
+      <c r="CS65" s="24" t="n"/>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
@@ -19851,6 +19922,7 @@
       <c r="CP66" s="24" t="n"/>
       <c r="CQ66" s="24" t="n"/>
       <c r="CR66" s="24" t="n"/>
+      <c r="CS66" s="24" t="n"/>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
@@ -20131,6 +20203,7 @@
       <c r="CP67" s="24" t="n"/>
       <c r="CQ67" s="24" t="n"/>
       <c r="CR67" s="24" t="n"/>
+      <c r="CS67" s="24" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
@@ -20411,6 +20484,7 @@
       <c r="CP68" s="24" t="n"/>
       <c r="CQ68" s="24" t="n"/>
       <c r="CR68" s="24" t="n"/>
+      <c r="CS68" s="24" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
@@ -20690,7 +20764,8 @@
       <c r="CO69" s="24" t="n"/>
       <c r="CP69" s="24" t="n"/>
       <c r="CQ69" s="24" t="n"/>
-      <c r="CR69" s="24" t="inlineStr">
+      <c r="CR69" s="24" t="n"/>
+      <c r="CS69" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -20974,7 +21049,8 @@
       <c r="CO70" s="24" t="n"/>
       <c r="CP70" s="24" t="n"/>
       <c r="CQ70" s="24" t="n"/>
-      <c r="CR70" s="24" t="inlineStr">
+      <c r="CR70" s="24" t="n"/>
+      <c r="CS70" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -21258,7 +21334,8 @@
       <c r="CO71" s="24" t="n"/>
       <c r="CP71" s="24" t="n"/>
       <c r="CQ71" s="24" t="n"/>
-      <c r="CR71" s="24" t="inlineStr">
+      <c r="CR71" s="24" t="n"/>
+      <c r="CS71" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -21542,7 +21619,8 @@
       <c r="CO72" s="24" t="n"/>
       <c r="CP72" s="24" t="n"/>
       <c r="CQ72" s="24" t="n"/>
-      <c r="CR72" s="24" t="inlineStr">
+      <c r="CR72" s="24" t="n"/>
+      <c r="CS72" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -21826,7 +21904,8 @@
       <c r="CO73" s="24" t="n"/>
       <c r="CP73" s="24" t="n"/>
       <c r="CQ73" s="24" t="n"/>
-      <c r="CR73" s="24" t="inlineStr">
+      <c r="CR73" s="24" t="n"/>
+      <c r="CS73" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -22110,7 +22189,8 @@
       <c r="CO74" s="24" t="n"/>
       <c r="CP74" s="24" t="n"/>
       <c r="CQ74" s="24" t="n"/>
-      <c r="CR74" s="24" t="inlineStr">
+      <c r="CR74" s="24" t="n"/>
+      <c r="CS74" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -22394,7 +22474,8 @@
       <c r="CO75" s="24" t="n"/>
       <c r="CP75" s="24" t="n"/>
       <c r="CQ75" s="24" t="n"/>
-      <c r="CR75" s="24" t="inlineStr">
+      <c r="CR75" s="24" t="n"/>
+      <c r="CS75" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -22678,7 +22759,8 @@
       <c r="CO76" s="24" t="n"/>
       <c r="CP76" s="24" t="n"/>
       <c r="CQ76" s="24" t="n"/>
-      <c r="CR76" s="24" t="inlineStr">
+      <c r="CR76" s="24" t="n"/>
+      <c r="CS76" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -22962,7 +23044,8 @@
       <c r="CO77" s="24" t="n"/>
       <c r="CP77" s="24" t="n"/>
       <c r="CQ77" s="24" t="n"/>
-      <c r="CR77" s="24" t="inlineStr">
+      <c r="CR77" s="24" t="n"/>
+      <c r="CS77" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -23246,7 +23329,8 @@
       <c r="CO78" s="24" t="n"/>
       <c r="CP78" s="24" t="n"/>
       <c r="CQ78" s="24" t="n"/>
-      <c r="CR78" s="24" t="inlineStr">
+      <c r="CR78" s="24" t="n"/>
+      <c r="CS78" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -23530,7 +23614,8 @@
       <c r="CO79" s="24" t="n"/>
       <c r="CP79" s="24" t="n"/>
       <c r="CQ79" s="24" t="n"/>
-      <c r="CR79" s="24" t="inlineStr">
+      <c r="CR79" s="24" t="n"/>
+      <c r="CS79" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -23814,7 +23899,8 @@
       <c r="CO80" s="24" t="n"/>
       <c r="CP80" s="24" t="n"/>
       <c r="CQ80" s="24" t="n"/>
-      <c r="CR80" s="24" t="inlineStr">
+      <c r="CR80" s="24" t="n"/>
+      <c r="CS80" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -24098,7 +24184,8 @@
       <c r="CO81" s="24" t="n"/>
       <c r="CP81" s="24" t="n"/>
       <c r="CQ81" s="24" t="n"/>
-      <c r="CR81" s="24" t="inlineStr">
+      <c r="CR81" s="24" t="n"/>
+      <c r="CS81" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -24382,7 +24469,8 @@
       <c r="CO82" s="24" t="n"/>
       <c r="CP82" s="24" t="n"/>
       <c r="CQ82" s="24" t="n"/>
-      <c r="CR82" s="24" t="inlineStr">
+      <c r="CR82" s="24" t="n"/>
+      <c r="CS82" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -24391,12 +24479,12 @@
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>6b9b9246d1ba456a</t>
+          <t>1085a28026374664</t>
         </is>
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:55:31.878300Z</t>
+          <t>2026-08-04T14:26:16.265665Z</t>
         </is>
       </c>
       <c r="C83" s="24" t="inlineStr">
@@ -24441,13 +24529,13 @@
         </is>
       </c>
       <c r="L83" s="26" t="n">
-        <v>-733</v>
+        <v>-669</v>
       </c>
       <c r="M83" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.149477</v>
       </c>
       <c r="N83" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.869961</v>
       </c>
       <c r="O83" s="28" t="n">
         <v>0.480757</v>
@@ -24456,7 +24544,7 @@
         <v>0.2</v>
       </c>
       <c r="Q83" s="28" t="n">
-        <v>-0.399195</v>
+        <v>-0.389204</v>
       </c>
       <c r="R83" s="26" t="n">
         <v>0</v>
@@ -24485,7 +24573,7 @@
       <c r="AD83" s="24" t="n"/>
       <c r="AE83" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.07 (home) / 1.59 (away) from EWMA attack/defense strengths. Executable ask 0.8800 (atc-clbf-nc-ars-2026-08-04-ars).</t>
+          <t>Poisson-DC rates 1.07 (home) / 1.59 (away) from EWMA attack/defense strengths. Executable ask 0.8700 (atc-clbf-nc-ars-2026-08-04-ars).</t>
         </is>
       </c>
       <c r="AF83" s="31" t="inlineStr">
@@ -24604,7 +24692,7 @@
       </c>
       <c r="BH83" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.570932Z</t>
+          <t>2026-08-04T14:23:20.588966Z</t>
         </is>
       </c>
       <c r="BI83" s="24" t="inlineStr">
@@ -24614,13 +24702,13 @@
       </c>
       <c r="BJ83" s="25" t="n"/>
       <c r="BK83" s="26" t="n">
-        <v>-733</v>
+        <v>-669</v>
       </c>
       <c r="BL83" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.149477</v>
       </c>
       <c r="BM83" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.869961</v>
       </c>
       <c r="BN83" s="28" t="n"/>
       <c r="BO83" s="28" t="n"/>
@@ -24652,7 +24740,8 @@
       <c r="CO83" s="24" t="n"/>
       <c r="CP83" s="24" t="n"/>
       <c r="CQ83" s="24" t="n"/>
-      <c r="CR83" s="24" t="inlineStr">
+      <c r="CR83" s="24" t="n"/>
+      <c r="CS83" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/flat/soccer.xlsx
+++ b/data/flat/soccer.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS83" headerRowCount="1">
-  <autoFilter ref="A1:CS83"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS88" headerRowCount="1">
+  <autoFilter ref="A1:CS88"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$83)</f>
+        <f>COUNTA('Picks'!$A$2:$A$88)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$83,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$88,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$83,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$88,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"win")+COUNTIFS('Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")+COUNTIFS('Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$83,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$88,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"win")/(COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"win")+COUNTIFS('Picks'!$BX$2:$BX$83,"&gt;0",'Picks'!$V$2:$V$83,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"win")/(COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"win")+COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$83)/SUM('Picks'!$BX$2:$BX$83),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$88)/SUM('Picks'!$BX$2:$BX$88),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$83)</f>
+        <f>SUM('Picks'!$BY$2:$BY$88)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$83,"&lt;&gt;",'Picks'!$AB$2:$AB$83),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$88,"&lt;&gt;",'Picks'!$AB$2:$AB$88),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$83,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$83,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$88,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$88,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$83,'Picks'!$AM$2:$AM$83,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$88,'Picks'!$AM$2:$AM$88,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$83,$A14,'Picks'!$U$2:$U$83,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$83,$A14,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$83,$A14,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$83,'Picks'!$H$2:$H$83,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$88,'Picks'!$H$2:$H$88,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$83,'Picks'!$H$2:$H$83,$A14,'Picks'!$U$2:$U$83,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$88,'Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$83,$A15,'Picks'!$U$2:$U$83,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$83,$A15,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$83,$A15,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$83,'Picks'!$H$2:$H$83,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$88,'Picks'!$H$2:$H$88,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$83,'Picks'!$H$2:$H$83,$A15,'Picks'!$U$2:$U$83,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$88,'Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$83,$A16,'Picks'!$U$2:$U$83,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$83,$A16,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$83,$A16,'Picks'!$U$2:$U$83,"settled",'Picks'!$V$2:$V$83,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$83,'Picks'!$H$2:$H$83,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$88,'Picks'!$H$2:$H$88,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$83,'Picks'!$H$2:$H$83,$A16,'Picks'!$U$2:$U$83,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$88,'Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS83"/>
+  <dimension ref="A1:CS88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24479,12 +24479,12 @@
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>1085a28026374664</t>
+          <t>0682c489cec848f9</t>
         </is>
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:16.265665Z</t>
+          <t>2026-08-04T16:53:20.897729Z</t>
         </is>
       </c>
       <c r="C83" s="24" t="inlineStr">
@@ -24529,13 +24529,13 @@
         </is>
       </c>
       <c r="L83" s="26" t="n">
-        <v>-669</v>
+        <v>-614</v>
       </c>
       <c r="M83" s="27" t="n">
-        <v>1.149477</v>
+        <v>1.162866</v>
       </c>
       <c r="N83" s="28" t="n">
-        <v>0.869961</v>
+        <v>0.859944</v>
       </c>
       <c r="O83" s="28" t="n">
         <v>0.480757</v>
@@ -24544,7 +24544,7 @@
         <v>0.2</v>
       </c>
       <c r="Q83" s="28" t="n">
-        <v>-0.389204</v>
+        <v>-0.379187</v>
       </c>
       <c r="R83" s="26" t="n">
         <v>0</v>
@@ -24559,21 +24559,35 @@
       </c>
       <c r="U83" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V83" s="24" t="n"/>
-      <c r="W83" s="26" t="n"/>
-      <c r="X83" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V83" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W83" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X83" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y83" s="25" t="n"/>
       <c r="Z83" s="26" t="n"/>
       <c r="AA83" s="28" t="n"/>
       <c r="AB83" s="28" t="n"/>
-      <c r="AC83" s="30" t="n"/>
-      <c r="AD83" s="24" t="n"/>
+      <c r="AC83" s="30" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="AD83" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:59:03.661368Z</t>
+        </is>
+      </c>
       <c r="AE83" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.07 (home) / 1.59 (away) from EWMA attack/defense strengths. Executable ask 0.8700 (atc-clbf-nc-ars-2026-08-04-ars).</t>
+          <t>Poisson-DC rates 1.07 (home) / 1.59 (away) from EWMA attack/defense strengths. Executable ask 0.8600 (atc-clbf-nc-ars-2026-08-04-ars).</t>
         </is>
       </c>
       <c r="AF83" s="31" t="inlineStr">
@@ -24692,7 +24706,7 @@
       </c>
       <c r="BH83" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:20.588966Z</t>
+          <t>2026-08-04T16:50:24.939028Z</t>
         </is>
       </c>
       <c r="BI83" s="24" t="inlineStr">
@@ -24702,13 +24716,13 @@
       </c>
       <c r="BJ83" s="25" t="n"/>
       <c r="BK83" s="26" t="n">
-        <v>-669</v>
+        <v>-614</v>
       </c>
       <c r="BL83" s="27" t="n">
-        <v>1.149477</v>
+        <v>1.162866</v>
       </c>
       <c r="BM83" s="28" t="n">
-        <v>0.869961</v>
+        <v>0.859944</v>
       </c>
       <c r="BN83" s="28" t="n"/>
       <c r="BO83" s="28" t="n"/>
@@ -24747,6 +24761,1361 @@
         </is>
       </c>
     </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>38727744850c4b8b</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:45.993524Z</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00Z</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>401841460</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I84" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J84" s="25" t="n"/>
+      <c r="K84" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L84" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M84" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N84" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O84" s="28" t="n">
+        <v>0.500109</v>
+      </c>
+      <c r="P84" s="28" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q84" s="28" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="R84" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U84" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V84" s="24" t="n"/>
+      <c r="W84" s="26" t="n"/>
+      <c r="X84" s="26" t="n"/>
+      <c r="Y84" s="25" t="n"/>
+      <c r="Z84" s="26" t="n"/>
+      <c r="AA84" s="28" t="n"/>
+      <c r="AB84" s="28" t="n"/>
+      <c r="AC84" s="30" t="n"/>
+      <c r="AD84" s="24" t="n"/>
+      <c r="AE84" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.66 (home) / 1.07 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-lpa-boc-est-2026-08-05-boc).</t>
+        </is>
+      </c>
+      <c r="AF84" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG84" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH84" s="24" t="n"/>
+      <c r="AI84" s="31" t="n"/>
+      <c r="AJ84" s="31" t="n"/>
+      <c r="AK84" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL84" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM84" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN84" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO84" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP84" s="24" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="AQ84" s="24" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="AR84" s="24" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="AS84" s="24" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="AT84" s="24" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="AU84" s="24" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="AV84" s="24" t="n"/>
+      <c r="AW84" s="24" t="n"/>
+      <c r="AX84" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY84" s="24" t="n"/>
+      <c r="AZ84" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA84" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB84" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC84" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD84" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE84" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF84" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG84" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH84" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:06.752018Z</t>
+        </is>
+      </c>
+      <c r="BI84" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ84" s="25" t="n"/>
+      <c r="BK84" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL84" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM84" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN84" s="28" t="n"/>
+      <c r="BO84" s="28" t="n"/>
+      <c r="BP84" s="25" t="n"/>
+      <c r="BQ84" s="27" t="n"/>
+      <c r="BR84" s="28" t="n"/>
+      <c r="BS84" s="28" t="n"/>
+      <c r="BT84" s="28" t="n"/>
+      <c r="BU84" s="25" t="n"/>
+      <c r="BV84" s="29" t="n"/>
+      <c r="BW84" s="24" t="n"/>
+      <c r="BX84" s="30" t="n"/>
+      <c r="BY84" s="27" t="n"/>
+      <c r="BZ84" s="24" t="n"/>
+      <c r="CA84" s="31" t="n"/>
+      <c r="CB84" s="24" t="n"/>
+      <c r="CC84" s="24" t="n"/>
+      <c r="CD84" s="24" t="n"/>
+      <c r="CE84" s="24" t="n"/>
+      <c r="CF84" s="24" t="n"/>
+      <c r="CG84" s="24" t="n"/>
+      <c r="CH84" s="24" t="n"/>
+      <c r="CI84" s="24" t="n"/>
+      <c r="CJ84" s="24" t="n"/>
+      <c r="CK84" s="24" t="n"/>
+      <c r="CL84" s="24" t="n"/>
+      <c r="CM84" s="24" t="n"/>
+      <c r="CN84" s="24" t="n"/>
+      <c r="CO84" s="24" t="n"/>
+      <c r="CP84" s="24" t="n"/>
+      <c r="CQ84" s="24" t="n"/>
+      <c r="CR84" s="24" t="n"/>
+      <c r="CS84" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>783d5ea3fb904bad</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:45.993524Z</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00Z</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>401843981</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J85" s="25" t="n"/>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L85" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M85" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N85" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O85" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P85" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q85" s="28" t="n">
+        <v>0.126102</v>
+      </c>
+      <c r="R85" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U85" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V85" s="24" t="n"/>
+      <c r="W85" s="26" t="n"/>
+      <c r="X85" s="26" t="n"/>
+      <c r="Y85" s="25" t="n"/>
+      <c r="Z85" s="26" t="n"/>
+      <c r="AA85" s="28" t="n"/>
+      <c r="AB85" s="28" t="n"/>
+      <c r="AC85" s="30" t="n"/>
+      <c r="AD85" s="24" t="n"/>
+      <c r="AE85" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-arg2-alm-gyt-2026-08-05-alm).</t>
+        </is>
+      </c>
+      <c r="AF85" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG85" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH85" s="24" t="n"/>
+      <c r="AI85" s="31" t="n"/>
+      <c r="AJ85" s="31" t="n"/>
+      <c r="AK85" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL85" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM85" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN85" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO85" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP85" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="AQ85" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="AR85" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="AS85" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="AT85" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="AU85" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="AV85" s="24" t="n"/>
+      <c r="AW85" s="24" t="n"/>
+      <c r="AX85" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY85" s="24" t="n"/>
+      <c r="AZ85" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA85" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB85" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC85" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD85" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE85" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF85" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG85" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH85" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:07.208609Z</t>
+        </is>
+      </c>
+      <c r="BI85" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ85" s="25" t="n"/>
+      <c r="BK85" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL85" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM85" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN85" s="28" t="n"/>
+      <c r="BO85" s="28" t="n"/>
+      <c r="BP85" s="25" t="n"/>
+      <c r="BQ85" s="27" t="n"/>
+      <c r="BR85" s="28" t="n"/>
+      <c r="BS85" s="28" t="n"/>
+      <c r="BT85" s="28" t="n"/>
+      <c r="BU85" s="25" t="n"/>
+      <c r="BV85" s="29" t="n"/>
+      <c r="BW85" s="24" t="n"/>
+      <c r="BX85" s="30" t="n"/>
+      <c r="BY85" s="27" t="n"/>
+      <c r="BZ85" s="24" t="n"/>
+      <c r="CA85" s="31" t="n"/>
+      <c r="CB85" s="24" t="n"/>
+      <c r="CC85" s="24" t="n"/>
+      <c r="CD85" s="24" t="n"/>
+      <c r="CE85" s="24" t="n"/>
+      <c r="CF85" s="24" t="n"/>
+      <c r="CG85" s="24" t="n"/>
+      <c r="CH85" s="24" t="n"/>
+      <c r="CI85" s="24" t="n"/>
+      <c r="CJ85" s="24" t="n"/>
+      <c r="CK85" s="24" t="n"/>
+      <c r="CL85" s="24" t="n"/>
+      <c r="CM85" s="24" t="n"/>
+      <c r="CN85" s="24" t="n"/>
+      <c r="CO85" s="24" t="n"/>
+      <c r="CP85" s="24" t="n"/>
+      <c r="CQ85" s="24" t="n"/>
+      <c r="CR85" s="24" t="n"/>
+      <c r="CS85" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="24" t="inlineStr">
+        <is>
+          <t>b4865df08a0b4db2</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:45.993524Z</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:00Z</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>401843990</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima (Jujuy)</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="H86" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I86" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J86" s="25" t="n"/>
+      <c r="K86" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L86" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M86" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N86" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O86" s="28" t="n">
+        <v>0.440521</v>
+      </c>
+      <c r="P86" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q86" s="28" t="n">
+        <v>-0.020308</v>
+      </c>
+      <c r="R86" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U86" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V86" s="24" t="n"/>
+      <c r="W86" s="26" t="n"/>
+      <c r="X86" s="26" t="n"/>
+      <c r="Y86" s="25" t="n"/>
+      <c r="Z86" s="26" t="n"/>
+      <c r="AA86" s="28" t="n"/>
+      <c r="AB86" s="28" t="n"/>
+      <c r="AC86" s="30" t="n"/>
+      <c r="AD86" s="24" t="n"/>
+      <c r="AE86" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.46 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-arg2-qui-ge-2026-08-05-qui).</t>
+        </is>
+      </c>
+      <c r="AF86" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG86" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH86" s="24" t="n"/>
+      <c r="AI86" s="31" t="n"/>
+      <c r="AJ86" s="31" t="n"/>
+      <c r="AK86" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL86" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM86" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN86" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO86" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP86" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima (Jujuy)</t>
+        </is>
+      </c>
+      <c r="AQ86" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima (Jujuy)</t>
+        </is>
+      </c>
+      <c r="AR86" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima (Jujuy)</t>
+        </is>
+      </c>
+      <c r="AS86" s="24" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="AT86" s="24" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="AU86" s="24" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="AV86" s="24" t="n"/>
+      <c r="AW86" s="24" t="n"/>
+      <c r="AX86" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY86" s="24" t="n"/>
+      <c r="AZ86" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA86" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB86" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC86" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD86" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE86" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF86" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG86" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH86" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:07.511498Z</t>
+        </is>
+      </c>
+      <c r="BI86" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ86" s="25" t="n"/>
+      <c r="BK86" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL86" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM86" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN86" s="28" t="n"/>
+      <c r="BO86" s="28" t="n"/>
+      <c r="BP86" s="25" t="n"/>
+      <c r="BQ86" s="27" t="n"/>
+      <c r="BR86" s="28" t="n"/>
+      <c r="BS86" s="28" t="n"/>
+      <c r="BT86" s="28" t="n"/>
+      <c r="BU86" s="25" t="n"/>
+      <c r="BV86" s="29" t="n"/>
+      <c r="BW86" s="24" t="n"/>
+      <c r="BX86" s="30" t="n"/>
+      <c r="BY86" s="27" t="n"/>
+      <c r="BZ86" s="24" t="n"/>
+      <c r="CA86" s="31" t="n"/>
+      <c r="CB86" s="24" t="n"/>
+      <c r="CC86" s="24" t="n"/>
+      <c r="CD86" s="24" t="n"/>
+      <c r="CE86" s="24" t="n"/>
+      <c r="CF86" s="24" t="n"/>
+      <c r="CG86" s="24" t="n"/>
+      <c r="CH86" s="24" t="n"/>
+      <c r="CI86" s="24" t="n"/>
+      <c r="CJ86" s="24" t="n"/>
+      <c r="CK86" s="24" t="n"/>
+      <c r="CL86" s="24" t="n"/>
+      <c r="CM86" s="24" t="n"/>
+      <c r="CN86" s="24" t="n"/>
+      <c r="CO86" s="24" t="n"/>
+      <c r="CP86" s="24" t="n"/>
+      <c r="CQ86" s="24" t="n"/>
+      <c r="CR86" s="24" t="n"/>
+      <c r="CS86" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>105e651231e64c23</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:45.993524Z</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:30Z</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>401871494</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F87" s="24" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J87" s="25" t="n"/>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L87" s="26" t="n">
+        <v>233</v>
+      </c>
+      <c r="M87" s="27" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N87" s="28" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="O87" s="28" t="n">
+        <v>0.483062</v>
+      </c>
+      <c r="P87" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q87" s="28" t="n">
+        <v>0.182762</v>
+      </c>
+      <c r="R87" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S87" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U87" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V87" s="24" t="n"/>
+      <c r="W87" s="26" t="n"/>
+      <c r="X87" s="26" t="n"/>
+      <c r="Y87" s="25" t="n"/>
+      <c r="Z87" s="26" t="n"/>
+      <c r="AA87" s="28" t="n"/>
+      <c r="AB87" s="28" t="n"/>
+      <c r="AC87" s="30" t="n"/>
+      <c r="AD87" s="24" t="n"/>
+      <c r="AE87" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.02 (home) / 1.55 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-clbf-cfc-juv-2026-08-05-juv).</t>
+        </is>
+      </c>
+      <c r="AF87" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG87" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH87" s="24" t="n"/>
+      <c r="AI87" s="31" t="n"/>
+      <c r="AJ87" s="31" t="n"/>
+      <c r="AK87" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL87" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM87" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN87" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO87" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP87" s="24" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="AQ87" s="24" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="AR87" s="24" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="AS87" s="24" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="AT87" s="24" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="AU87" s="24" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="AV87" s="24" t="n"/>
+      <c r="AW87" s="24" t="n"/>
+      <c r="AX87" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY87" s="24" t="n"/>
+      <c r="AZ87" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA87" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB87" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC87" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD87" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE87" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF87" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG87" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH87" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:08.269054Z</t>
+        </is>
+      </c>
+      <c r="BI87" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ87" s="25" t="n"/>
+      <c r="BK87" s="26" t="n">
+        <v>233</v>
+      </c>
+      <c r="BL87" s="27" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BM87" s="28" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BN87" s="28" t="n"/>
+      <c r="BO87" s="28" t="n"/>
+      <c r="BP87" s="25" t="n"/>
+      <c r="BQ87" s="27" t="n"/>
+      <c r="BR87" s="28" t="n"/>
+      <c r="BS87" s="28" t="n"/>
+      <c r="BT87" s="28" t="n"/>
+      <c r="BU87" s="25" t="n"/>
+      <c r="BV87" s="29" t="n"/>
+      <c r="BW87" s="24" t="n"/>
+      <c r="BX87" s="30" t="n"/>
+      <c r="BY87" s="27" t="n"/>
+      <c r="BZ87" s="24" t="n"/>
+      <c r="CA87" s="31" t="n"/>
+      <c r="CB87" s="24" t="n"/>
+      <c r="CC87" s="24" t="n"/>
+      <c r="CD87" s="24" t="n"/>
+      <c r="CE87" s="24" t="n"/>
+      <c r="CF87" s="24" t="n"/>
+      <c r="CG87" s="24" t="n"/>
+      <c r="CH87" s="24" t="n"/>
+      <c r="CI87" s="24" t="n"/>
+      <c r="CJ87" s="24" t="n"/>
+      <c r="CK87" s="24" t="n"/>
+      <c r="CL87" s="24" t="n"/>
+      <c r="CM87" s="24" t="n"/>
+      <c r="CN87" s="24" t="n"/>
+      <c r="CO87" s="24" t="n"/>
+      <c r="CP87" s="24" t="n"/>
+      <c r="CQ87" s="24" t="n"/>
+      <c r="CR87" s="24" t="n"/>
+      <c r="CS87" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>507231a5801040c4</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:45.993524Z</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:30Z</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>401867142</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="H88" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I88" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J88" s="25" t="n"/>
+      <c r="K88" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L88" s="26" t="n">
+        <v>-270</v>
+      </c>
+      <c r="M88" s="27" t="n">
+        <v>1.37037</v>
+      </c>
+      <c r="N88" s="28" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="O88" s="28" t="n">
+        <v>0.615056</v>
+      </c>
+      <c r="P88" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q88" s="28" t="n">
+        <v>-0.114674</v>
+      </c>
+      <c r="R88" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T88" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U88" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V88" s="24" t="n"/>
+      <c r="W88" s="26" t="n"/>
+      <c r="X88" s="26" t="n"/>
+      <c r="Y88" s="25" t="n"/>
+      <c r="Z88" s="26" t="n"/>
+      <c r="AA88" s="28" t="n"/>
+      <c r="AB88" s="28" t="n"/>
+      <c r="AC88" s="30" t="n"/>
+      <c r="AD88" s="24" t="n"/>
+      <c r="AE88" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.70 (home) / 0.66 (away) from EWMA attack/defense strengths. Executable ask 0.7300 (atc-clbf-afr-rbb-2026-08-05-afr).</t>
+        </is>
+      </c>
+      <c r="AF88" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG88" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH88" s="24" t="n"/>
+      <c r="AI88" s="31" t="n"/>
+      <c r="AJ88" s="31" t="n"/>
+      <c r="AK88" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL88" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM88" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN88" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO88" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP88" s="24" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="AQ88" s="24" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="AR88" s="24" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="AS88" s="24" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="AT88" s="24" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="AU88" s="24" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="AV88" s="24" t="n"/>
+      <c r="AW88" s="24" t="n"/>
+      <c r="AX88" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY88" s="24" t="n"/>
+      <c r="AZ88" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA88" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB88" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC88" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD88" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE88" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF88" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG88" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH88" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:09.148998Z</t>
+        </is>
+      </c>
+      <c r="BI88" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ88" s="25" t="n"/>
+      <c r="BK88" s="26" t="n">
+        <v>-270</v>
+      </c>
+      <c r="BL88" s="27" t="n">
+        <v>1.37037</v>
+      </c>
+      <c r="BM88" s="28" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="BN88" s="28" t="n"/>
+      <c r="BO88" s="28" t="n"/>
+      <c r="BP88" s="25" t="n"/>
+      <c r="BQ88" s="27" t="n"/>
+      <c r="BR88" s="28" t="n"/>
+      <c r="BS88" s="28" t="n"/>
+      <c r="BT88" s="28" t="n"/>
+      <c r="BU88" s="25" t="n"/>
+      <c r="BV88" s="29" t="n"/>
+      <c r="BW88" s="24" t="n"/>
+      <c r="BX88" s="30" t="n"/>
+      <c r="BY88" s="27" t="n"/>
+      <c r="BZ88" s="24" t="n"/>
+      <c r="CA88" s="31" t="n"/>
+      <c r="CB88" s="24" t="n"/>
+      <c r="CC88" s="24" t="n"/>
+      <c r="CD88" s="24" t="n"/>
+      <c r="CE88" s="24" t="n"/>
+      <c r="CF88" s="24" t="n"/>
+      <c r="CG88" s="24" t="n"/>
+      <c r="CH88" s="24" t="n"/>
+      <c r="CI88" s="24" t="n"/>
+      <c r="CJ88" s="24" t="n"/>
+      <c r="CK88" s="24" t="n"/>
+      <c r="CL88" s="24" t="n"/>
+      <c r="CM88" s="24" t="n"/>
+      <c r="CN88" s="24" t="n"/>
+      <c r="CO88" s="24" t="n"/>
+      <c r="CP88" s="24" t="n"/>
+      <c r="CQ88" s="24" t="n"/>
+      <c r="CR88" s="24" t="n"/>
+      <c r="CS88" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/flat/soccer.xlsx
+++ b/data/flat/soccer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -24764,22 +24764,22 @@
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
         <is>
-          <t>38727744850c4b8b</t>
+          <t>59c4be4e115e4c99</t>
         </is>
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:45.993524Z</t>
+          <t>2026-08-05T10:45:53.298989Z</t>
         </is>
       </c>
       <c r="C84" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00Z</t>
+          <t>2026-08-05T11:30Z</t>
         </is>
       </c>
       <c r="D84" s="24" t="inlineStr">
         <is>
-          <t>401841460</t>
+          <t>401871494</t>
         </is>
       </c>
       <c r="E84" s="24" t="inlineStr">
@@ -24789,12 +24789,12 @@
       </c>
       <c r="F84" s="24" t="inlineStr">
         <is>
-          <t>Estudiantes de La Plata</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G84" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="H84" s="24" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="I84" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J84" s="25" t="n"/>
@@ -24814,25 +24814,25 @@
         </is>
       </c>
       <c r="L84" s="26" t="n">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="M84" s="27" t="n">
-        <v>2.17</v>
+        <v>3.33</v>
       </c>
       <c r="N84" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.3003</v>
       </c>
       <c r="O84" s="28" t="n">
-        <v>0.500109</v>
+        <v>0.483062</v>
       </c>
       <c r="P84" s="28" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="Q84" s="28" t="n">
-        <v>0.03928</v>
+        <v>0.182762</v>
       </c>
       <c r="R84" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S84" s="29" t="n">
         <v>1</v>
@@ -24844,21 +24844,35 @@
       </c>
       <c r="U84" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V84" s="24" t="n"/>
-      <c r="W84" s="26" t="n"/>
-      <c r="X84" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V84" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W84" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X84" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y84" s="25" t="n"/>
       <c r="Z84" s="26" t="n"/>
       <c r="AA84" s="28" t="n"/>
       <c r="AB84" s="28" t="n"/>
-      <c r="AC84" s="30" t="n"/>
-      <c r="AD84" s="24" t="n"/>
+      <c r="AC84" s="30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD84" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:50:15.913809Z</t>
+        </is>
+      </c>
       <c r="AE84" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.66 (home) / 1.07 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-lpa-boc-est-2026-08-05-boc).</t>
+          <t>Poisson-DC rates 1.02 (home) / 1.55 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-clbf-cfc-juv-2026-08-05-juv).</t>
         </is>
       </c>
       <c r="AF84" s="31" t="inlineStr">
@@ -24894,37 +24908,37 @@
       </c>
       <c r="AO84" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP84" s="24" t="inlineStr">
         <is>
-          <t>Estudiantes de La Plata</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="AQ84" s="24" t="inlineStr">
         <is>
-          <t>Estudiantes de La Plata</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="AR84" s="24" t="inlineStr">
         <is>
-          <t>Estudiantes de La Plata</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="AS84" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AT84" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AU84" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="AV84" s="24" t="n"/>
@@ -24977,7 +24991,7 @@
       </c>
       <c r="BH84" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:06.752018Z</t>
+          <t>2026-08-05T10:42:33.963889Z</t>
         </is>
       </c>
       <c r="BI84" s="24" t="inlineStr">
@@ -24987,13 +25001,13 @@
       </c>
       <c r="BJ84" s="25" t="n"/>
       <c r="BK84" s="26" t="n">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="BL84" s="27" t="n">
-        <v>2.17</v>
+        <v>3.33</v>
       </c>
       <c r="BM84" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.3003</v>
       </c>
       <c r="BN84" s="28" t="n"/>
       <c r="BO84" s="28" t="n"/>
@@ -25035,22 +25049,22 @@
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>783d5ea3fb904bad</t>
+          <t>fbdaec01e3d74d51</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:45.993524Z</t>
+          <t>2026-08-05T13:55:50.543648Z</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T22:00Z</t>
         </is>
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>401843981</t>
+          <t>401841460</t>
         </is>
       </c>
       <c r="E85" s="24" t="inlineStr">
@@ -25060,12 +25074,12 @@
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Estudiantes de La Plata</t>
         </is>
       </c>
       <c r="G85" s="24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr">
@@ -25085,22 +25099,22 @@
         </is>
       </c>
       <c r="L85" s="26" t="n">
-        <v>203</v>
+        <v>117</v>
       </c>
       <c r="M85" s="27" t="n">
-        <v>3.03</v>
+        <v>2.17</v>
       </c>
       <c r="N85" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.460829</v>
       </c>
       <c r="O85" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.500109</v>
       </c>
       <c r="P85" s="28" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Q85" s="28" t="n">
-        <v>0.126102</v>
+        <v>0.03928</v>
       </c>
       <c r="R85" s="26" t="n">
         <v>0</v>
@@ -25129,7 +25143,7 @@
       <c r="AD85" s="24" t="n"/>
       <c r="AE85" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-arg2-alm-gyt-2026-08-05-alm).</t>
+          <t>Poisson-DC rates 1.66 (home) / 1.07 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-lpa-boc-est-2026-08-05-boc).</t>
         </is>
       </c>
       <c r="AF85" s="31" t="inlineStr">
@@ -25170,32 +25184,32 @@
       </c>
       <c r="AP85" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Estudiantes de La Plata</t>
         </is>
       </c>
       <c r="AQ85" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Estudiantes de La Plata</t>
         </is>
       </c>
       <c r="AR85" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Estudiantes de La Plata</t>
         </is>
       </c>
       <c r="AS85" s="24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AT85" s="24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AU85" s="24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AV85" s="24" t="n"/>
@@ -25248,7 +25262,7 @@
       </c>
       <c r="BH85" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:07.208609Z</t>
+          <t>2026-08-05T13:52:36.521797Z</t>
         </is>
       </c>
       <c r="BI85" s="24" t="inlineStr">
@@ -25258,13 +25272,13 @@
       </c>
       <c r="BJ85" s="25" t="n"/>
       <c r="BK85" s="26" t="n">
-        <v>203</v>
+        <v>117</v>
       </c>
       <c r="BL85" s="27" t="n">
-        <v>3.03</v>
+        <v>2.17</v>
       </c>
       <c r="BM85" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.460829</v>
       </c>
       <c r="BN85" s="28" t="n"/>
       <c r="BO85" s="28" t="n"/>
@@ -25306,22 +25320,22 @@
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="24" t="inlineStr">
         <is>
-          <t>b4865df08a0b4db2</t>
+          <t>11d60a53b30247fd</t>
         </is>
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:45.993524Z</t>
+          <t>2026-08-05T13:55:50.543648Z</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T23:00Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D86" s="24" t="inlineStr">
         <is>
-          <t>401843990</t>
+          <t>401843981</t>
         </is>
       </c>
       <c r="E86" s="24" t="inlineStr">
@@ -25331,12 +25345,12 @@
       </c>
       <c r="F86" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima (Jujuy)</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="G86" s="24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="H86" s="24" t="inlineStr">
@@ -25356,22 +25370,22 @@
         </is>
       </c>
       <c r="L86" s="26" t="n">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="M86" s="27" t="n">
-        <v>2.17</v>
+        <v>3.03</v>
       </c>
       <c r="N86" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.330033</v>
       </c>
       <c r="O86" s="28" t="n">
-        <v>0.440521</v>
+        <v>0.456135</v>
       </c>
       <c r="P86" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q86" s="28" t="n">
-        <v>-0.020308</v>
+        <v>0.126102</v>
       </c>
       <c r="R86" s="26" t="n">
         <v>0</v>
@@ -25400,7 +25414,7 @@
       <c r="AD86" s="24" t="n"/>
       <c r="AE86" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.46 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-arg2-qui-ge-2026-08-05-qui).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-arg2-alm-gyt-2026-08-05-alm).</t>
         </is>
       </c>
       <c r="AF86" s="31" t="inlineStr">
@@ -25441,32 +25455,32 @@
       </c>
       <c r="AP86" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima (Jujuy)</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AQ86" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima (Jujuy)</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AR86" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima (Jujuy)</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AS86" s="24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="AT86" s="24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="AU86" s="24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="AV86" s="24" t="n"/>
@@ -25519,7 +25533,7 @@
       </c>
       <c r="BH86" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:07.511498Z</t>
+          <t>2026-08-05T13:52:36.609124Z</t>
         </is>
       </c>
       <c r="BI86" s="24" t="inlineStr">
@@ -25529,13 +25543,13 @@
       </c>
       <c r="BJ86" s="25" t="n"/>
       <c r="BK86" s="26" t="n">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="BL86" s="27" t="n">
-        <v>2.17</v>
+        <v>3.03</v>
       </c>
       <c r="BM86" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.330033</v>
       </c>
       <c r="BN86" s="28" t="n"/>
       <c r="BO86" s="28" t="n"/>
@@ -25570,29 +25584,29 @@
       <c r="CR86" s="24" t="n"/>
       <c r="CS86" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>105e651231e64c23</t>
+          <t>cd1d25a8563f4b94</t>
         </is>
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:45.993524Z</t>
+          <t>2026-08-05T13:55:50.543648Z</t>
         </is>
       </c>
       <c r="C87" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T11:30Z</t>
+          <t>2026-08-05T18:30Z</t>
         </is>
       </c>
       <c r="D87" s="24" t="inlineStr">
         <is>
-          <t>401871494</t>
+          <t>401867142</t>
         </is>
       </c>
       <c r="E87" s="24" t="inlineStr">
@@ -25602,12 +25616,12 @@
       </c>
       <c r="F87" s="24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G87" s="24" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="H87" s="24" t="inlineStr">
@@ -25617,7 +25631,7 @@
       </c>
       <c r="I87" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J87" s="25" t="n"/>
@@ -25627,28 +25641,28 @@
         </is>
       </c>
       <c r="L87" s="26" t="n">
-        <v>233</v>
+        <v>-170</v>
       </c>
       <c r="M87" s="27" t="n">
-        <v>3.33</v>
+        <v>1.588235</v>
       </c>
       <c r="N87" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.62963</v>
       </c>
       <c r="O87" s="28" t="n">
-        <v>0.483062</v>
+        <v>0.615056</v>
       </c>
       <c r="P87" s="28" t="n">
         <v>0.04</v>
       </c>
       <c r="Q87" s="28" t="n">
-        <v>0.182762</v>
+        <v>-0.014574</v>
       </c>
       <c r="R87" s="26" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="S87" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T87" s="24" t="inlineStr">
         <is>
@@ -25671,7 +25685,7 @@
       <c r="AD87" s="24" t="n"/>
       <c r="AE87" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.02 (home) / 1.55 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-clbf-cfc-juv-2026-08-05-juv).</t>
+          <t>Poisson-DC rates 1.70 (home) / 0.66 (away) from EWMA attack/defense strengths. Executable ask 0.6300 (atc-clbf-afr-rbb-2026-08-05-afr).</t>
         </is>
       </c>
       <c r="AF87" s="31" t="inlineStr">
@@ -25712,32 +25726,32 @@
       </c>
       <c r="AP87" s="24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="AQ87" s="24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="AR87" s="24" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="AS87" s="24" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AT87" s="24" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AU87" s="24" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AV87" s="24" t="n"/>
@@ -25790,7 +25804,7 @@
       </c>
       <c r="BH87" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:08.269054Z</t>
+          <t>2026-08-05T13:52:37.515931Z</t>
         </is>
       </c>
       <c r="BI87" s="24" t="inlineStr">
@@ -25800,13 +25814,13 @@
       </c>
       <c r="BJ87" s="25" t="n"/>
       <c r="BK87" s="26" t="n">
-        <v>233</v>
+        <v>-170</v>
       </c>
       <c r="BL87" s="27" t="n">
-        <v>3.33</v>
+        <v>1.588235</v>
       </c>
       <c r="BM87" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.62963</v>
       </c>
       <c r="BN87" s="28" t="n"/>
       <c r="BO87" s="28" t="n"/>
@@ -25841,29 +25855,29 @@
       <c r="CR87" s="24" t="n"/>
       <c r="CS87" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
         <is>
-          <t>507231a5801040c4</t>
+          <t>96772a5ab79f472c</t>
         </is>
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:45.993524Z</t>
+          <t>2026-08-05T13:55:50.543648Z</t>
         </is>
       </c>
       <c r="C88" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:30Z</t>
+          <t>2026-08-05T19:00Z</t>
         </is>
       </c>
       <c r="D88" s="24" t="inlineStr">
         <is>
-          <t>401867142</t>
+          <t>401886451</t>
         </is>
       </c>
       <c r="E88" s="24" t="inlineStr">
@@ -25873,12 +25887,12 @@
       </c>
       <c r="F88" s="24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="G88" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H88" s="24" t="inlineStr">
@@ -25888,7 +25902,7 @@
       </c>
       <c r="I88" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J88" s="25" t="n"/>
@@ -25898,28 +25912,28 @@
         </is>
       </c>
       <c r="L88" s="26" t="n">
-        <v>-270</v>
+        <v>100</v>
       </c>
       <c r="M88" s="27" t="n">
-        <v>1.37037</v>
+        <v>2</v>
       </c>
       <c r="N88" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.5</v>
       </c>
       <c r="O88" s="28" t="n">
-        <v>0.615056</v>
+        <v>0.526434</v>
       </c>
       <c r="P88" s="28" t="n">
         <v>0.04</v>
       </c>
       <c r="Q88" s="28" t="n">
-        <v>-0.114674</v>
+        <v>0.026434</v>
       </c>
       <c r="R88" s="26" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="S88" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T88" s="24" t="inlineStr">
         <is>
@@ -25942,7 +25956,7 @@
       <c r="AD88" s="24" t="n"/>
       <c r="AE88" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.70 (home) / 0.66 (away) from EWMA attack/defense strengths. Executable ask 0.7300 (atc-clbf-afr-rbb-2026-08-05-afr).</t>
+          <t>Poisson-DC rates 1.11 (home) / 1.81 (away) from EWMA attack/defense strengths. Executable ask 0.5000 (atc-clbf-mal-psg-2026-08-05-psg).</t>
         </is>
       </c>
       <c r="AF88" s="31" t="inlineStr">
@@ -25983,32 +25997,32 @@
       </c>
       <c r="AP88" s="24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="AQ88" s="24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="AR88" s="24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="AS88" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="AT88" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="AU88" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="AV88" s="24" t="n"/>
@@ -26061,7 +26075,7 @@
       </c>
       <c r="BH88" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:09.148998Z</t>
+          <t>2026-08-05T13:52:37.762719Z</t>
         </is>
       </c>
       <c r="BI88" s="24" t="inlineStr">
@@ -26071,13 +26085,13 @@
       </c>
       <c r="BJ88" s="25" t="n"/>
       <c r="BK88" s="26" t="n">
-        <v>-270</v>
+        <v>100</v>
       </c>
       <c r="BL88" s="27" t="n">
-        <v>1.37037</v>
+        <v>2</v>
       </c>
       <c r="BM88" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.5</v>
       </c>
       <c r="BN88" s="28" t="n"/>
       <c r="BO88" s="28" t="n"/>
@@ -26112,7 +26126,7 @@
       <c r="CR88" s="24" t="n"/>
       <c r="CS88" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/data/flat/soccer.xlsx
+++ b/data/flat/soccer.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS88" headerRowCount="1">
-  <autoFilter ref="A1:CS88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS95" headerRowCount="1">
+  <autoFilter ref="A1:CS95"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$88)</f>
+        <f>COUNTA('Picks'!$A$2:$A$95)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$88,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$95,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$95,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")+COUNTIFS('Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$95,"settled",'Picks'!$V$2:$V$95,"win")+COUNTIFS('Picks'!$U$2:$U$95,"settled",'Picks'!$V$2:$V$95,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$88,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$95,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$95,"&gt;0",'Picks'!$V$2:$V$95,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$95,"&gt;0",'Picks'!$V$2:$V$95,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"win")/(COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"win")+COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$95,"&gt;0",'Picks'!$V$2:$V$95,"win")/(COUNTIFS('Picks'!$BX$2:$BX$95,"&gt;0",'Picks'!$V$2:$V$95,"win")+COUNTIFS('Picks'!$BX$2:$BX$95,"&gt;0",'Picks'!$V$2:$V$95,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$88)/SUM('Picks'!$BX$2:$BX$88),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$95)/SUM('Picks'!$BX$2:$BX$95),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$88)</f>
+        <f>SUM('Picks'!$BY$2:$BY$95)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$88,"&lt;&gt;",'Picks'!$AB$2:$AB$88),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$95,"&lt;&gt;",'Picks'!$AB$2:$AB$95),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$88,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$95,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$95,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$88,'Picks'!$AM$2:$AM$88,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$95,'Picks'!$AM$2:$AM$95,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$95,$A14,'Picks'!$U$2:$U$95,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$95,$A14,'Picks'!$U$2:$U$95,"settled",'Picks'!$V$2:$V$95,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$95,$A14,'Picks'!$U$2:$U$95,"settled",'Picks'!$V$2:$V$95,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$88,'Picks'!$H$2:$H$88,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$95,'Picks'!$H$2:$H$95,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$88,'Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$95,'Picks'!$H$2:$H$95,$A14,'Picks'!$U$2:$U$95,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$95,$A15,'Picks'!$U$2:$U$95,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$95,$A15,'Picks'!$U$2:$U$95,"settled",'Picks'!$V$2:$V$95,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$95,$A15,'Picks'!$U$2:$U$95,"settled",'Picks'!$V$2:$V$95,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$88,'Picks'!$H$2:$H$88,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$95,'Picks'!$H$2:$H$95,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$88,'Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$95,'Picks'!$H$2:$H$95,$A15,'Picks'!$U$2:$U$95,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$95,$A16,'Picks'!$U$2:$U$95,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$95,$A16,'Picks'!$U$2:$U$95,"settled",'Picks'!$V$2:$V$95,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$95,$A16,'Picks'!$U$2:$U$95,"settled",'Picks'!$V$2:$V$95,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$88,'Picks'!$H$2:$H$88,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$95,'Picks'!$H$2:$H$95,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$88,'Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$95,'Picks'!$H$2:$H$95,$A16,'Picks'!$U$2:$U$95,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS88"/>
+  <dimension ref="A1:CS95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -25049,22 +25049,22 @@
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>fbdaec01e3d74d51</t>
+          <t>d0a8fc4bf3eb49b5</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:55:50.543648Z</t>
+          <t>2026-08-05T17:03:58.301897Z</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>401841460</t>
+          <t>401843981</t>
         </is>
       </c>
       <c r="E85" s="24" t="inlineStr">
@@ -25074,12 +25074,12 @@
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
-          <t>Estudiantes de La Plata</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="G85" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr">
@@ -25099,28 +25099,28 @@
         </is>
       </c>
       <c r="L85" s="26" t="n">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="M85" s="27" t="n">
-        <v>2.17</v>
+        <v>3.03</v>
       </c>
       <c r="N85" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.330033</v>
       </c>
       <c r="O85" s="28" t="n">
-        <v>0.500109</v>
+        <v>0.456135</v>
       </c>
       <c r="P85" s="28" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="Q85" s="28" t="n">
-        <v>0.03928</v>
+        <v>0.126102</v>
       </c>
       <c r="R85" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S85" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T85" s="24" t="inlineStr">
         <is>
@@ -25129,21 +25129,35 @@
       </c>
       <c r="U85" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V85" s="24" t="n"/>
-      <c r="W85" s="26" t="n"/>
-      <c r="X85" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V85" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W85" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X85" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y85" s="25" t="n"/>
       <c r="Z85" s="26" t="n"/>
       <c r="AA85" s="28" t="n"/>
       <c r="AB85" s="28" t="n"/>
-      <c r="AC85" s="30" t="n"/>
-      <c r="AD85" s="24" t="n"/>
+      <c r="AC85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:47.753158Z</t>
+        </is>
+      </c>
       <c r="AE85" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.66 (home) / 1.07 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-lpa-boc-est-2026-08-05-boc).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-arg2-alm-gyt-2026-08-05-alm).</t>
         </is>
       </c>
       <c r="AF85" s="31" t="inlineStr">
@@ -25153,7 +25167,7 @@
       </c>
       <c r="AG85" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH85" s="24" t="n"/>
@@ -25179,37 +25193,37 @@
       </c>
       <c r="AO85" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP85" s="24" t="inlineStr">
         <is>
-          <t>Estudiantes de La Plata</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AQ85" s="24" t="inlineStr">
         <is>
-          <t>Estudiantes de La Plata</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AR85" s="24" t="inlineStr">
         <is>
-          <t>Estudiantes de La Plata</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AS85" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="AT85" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="AU85" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="AV85" s="24" t="n"/>
@@ -25262,7 +25276,7 @@
       </c>
       <c r="BH85" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:36.521797Z</t>
+          <t>2026-08-05T17:01:54.694147Z</t>
         </is>
       </c>
       <c r="BI85" s="24" t="inlineStr">
@@ -25272,13 +25286,13 @@
       </c>
       <c r="BJ85" s="25" t="n"/>
       <c r="BK85" s="26" t="n">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="BL85" s="27" t="n">
-        <v>2.17</v>
+        <v>3.03</v>
       </c>
       <c r="BM85" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.330033</v>
       </c>
       <c r="BN85" s="28" t="n"/>
       <c r="BO85" s="28" t="n"/>
@@ -25320,22 +25334,22 @@
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="24" t="inlineStr">
         <is>
-          <t>11d60a53b30247fd</t>
+          <t>0c24c70c0c3c47c4</t>
         </is>
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:55:50.543648Z</t>
+          <t>2026-08-05T17:03:58.301897Z</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T18:30Z</t>
         </is>
       </c>
       <c r="D86" s="24" t="inlineStr">
         <is>
-          <t>401843981</t>
+          <t>401867142</t>
         </is>
       </c>
       <c r="E86" s="24" t="inlineStr">
@@ -25345,12 +25359,12 @@
       </c>
       <c r="F86" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G86" s="24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="H86" s="24" t="inlineStr">
@@ -25370,51 +25384,65 @@
         </is>
       </c>
       <c r="L86" s="26" t="n">
-        <v>203</v>
+        <v>-194</v>
       </c>
       <c r="M86" s="27" t="n">
-        <v>3.03</v>
+        <v>1.515464</v>
       </c>
       <c r="N86" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.659864</v>
       </c>
       <c r="O86" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.615056</v>
       </c>
       <c r="P86" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q86" s="28" t="n">
-        <v>0.126102</v>
+        <v>-0.044808</v>
       </c>
       <c r="R86" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S86" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="29" t="n">
+      <c r="T86" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U86" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V86" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W86" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X86" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T86" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U86" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V86" s="24" t="n"/>
-      <c r="W86" s="26" t="n"/>
-      <c r="X86" s="26" t="n"/>
       <c r="Y86" s="25" t="n"/>
       <c r="Z86" s="26" t="n"/>
       <c r="AA86" s="28" t="n"/>
       <c r="AB86" s="28" t="n"/>
-      <c r="AC86" s="30" t="n"/>
-      <c r="AD86" s="24" t="n"/>
+      <c r="AC86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:58:28.792815Z</t>
+        </is>
+      </c>
       <c r="AE86" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-arg2-alm-gyt-2026-08-05-alm).</t>
+          <t>Poisson-DC rates 1.70 (home) / 0.66 (away) from EWMA attack/defense strengths. Executable ask 0.6600 (atc-clbf-afr-rbb-2026-08-05-afr).</t>
         </is>
       </c>
       <c r="AF86" s="31" t="inlineStr">
@@ -25424,7 +25452,7 @@
       </c>
       <c r="AG86" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH86" s="24" t="n"/>
@@ -25450,37 +25478,37 @@
       </c>
       <c r="AO86" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP86" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="AQ86" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="AR86" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="AS86" s="24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AT86" s="24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AU86" s="24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AV86" s="24" t="n"/>
@@ -25533,7 +25561,7 @@
       </c>
       <c r="BH86" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:36.609124Z</t>
+          <t>2026-08-05T17:01:55.596249Z</t>
         </is>
       </c>
       <c r="BI86" s="24" t="inlineStr">
@@ -25543,13 +25571,13 @@
       </c>
       <c r="BJ86" s="25" t="n"/>
       <c r="BK86" s="26" t="n">
-        <v>203</v>
+        <v>-194</v>
       </c>
       <c r="BL86" s="27" t="n">
-        <v>3.03</v>
+        <v>1.515464</v>
       </c>
       <c r="BM86" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.659864</v>
       </c>
       <c r="BN86" s="28" t="n"/>
       <c r="BO86" s="28" t="n"/>
@@ -25584,29 +25612,29 @@
       <c r="CR86" s="24" t="n"/>
       <c r="CS86" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>cd1d25a8563f4b94</t>
+          <t>331dab6fce6540c2</t>
         </is>
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:55:50.543648Z</t>
+          <t>2026-08-05T17:03:58.301897Z</t>
         </is>
       </c>
       <c r="C87" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:30Z</t>
+          <t>2026-08-05T19:00Z</t>
         </is>
       </c>
       <c r="D87" s="24" t="inlineStr">
         <is>
-          <t>401867142</t>
+          <t>401886451</t>
         </is>
       </c>
       <c r="E87" s="24" t="inlineStr">
@@ -25616,12 +25644,12 @@
       </c>
       <c r="F87" s="24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="G87" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H87" s="24" t="inlineStr">
@@ -25631,7 +25659,7 @@
       </c>
       <c r="I87" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J87" s="25" t="n"/>
@@ -25641,28 +25669,28 @@
         </is>
       </c>
       <c r="L87" s="26" t="n">
-        <v>-170</v>
+        <v>104</v>
       </c>
       <c r="M87" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.04</v>
       </c>
       <c r="N87" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.490196</v>
       </c>
       <c r="O87" s="28" t="n">
-        <v>0.615056</v>
+        <v>0.526434</v>
       </c>
       <c r="P87" s="28" t="n">
         <v>0.04</v>
       </c>
       <c r="Q87" s="28" t="n">
-        <v>-0.014574</v>
+        <v>0.036238</v>
       </c>
       <c r="R87" s="26" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="S87" s="29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T87" s="24" t="inlineStr">
         <is>
@@ -25671,21 +25699,35 @@
       </c>
       <c r="U87" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V87" s="24" t="n"/>
-      <c r="W87" s="26" t="n"/>
-      <c r="X87" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V87" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W87" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y87" s="25" t="n"/>
       <c r="Z87" s="26" t="n"/>
       <c r="AA87" s="28" t="n"/>
       <c r="AB87" s="28" t="n"/>
-      <c r="AC87" s="30" t="n"/>
-      <c r="AD87" s="24" t="n"/>
+      <c r="AC87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:58:29.328168Z</t>
+        </is>
+      </c>
       <c r="AE87" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.70 (home) / 0.66 (away) from EWMA attack/defense strengths. Executable ask 0.6300 (atc-clbf-afr-rbb-2026-08-05-afr).</t>
+          <t>Poisson-DC rates 1.11 (home) / 1.81 (away) from EWMA attack/defense strengths. Executable ask 0.4900 (atc-clbf-mal-psg-2026-08-05-psg).</t>
         </is>
       </c>
       <c r="AF87" s="31" t="inlineStr">
@@ -25695,7 +25737,7 @@
       </c>
       <c r="AG87" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH87" s="24" t="n"/>
@@ -25721,37 +25763,37 @@
       </c>
       <c r="AO87" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP87" s="24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="AQ87" s="24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="AR87" s="24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="AS87" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="AT87" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="AU87" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="AV87" s="24" t="n"/>
@@ -25804,7 +25846,7 @@
       </c>
       <c r="BH87" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:37.515931Z</t>
+          <t>2026-08-05T17:01:55.733913Z</t>
         </is>
       </c>
       <c r="BI87" s="24" t="inlineStr">
@@ -25814,13 +25856,13 @@
       </c>
       <c r="BJ87" s="25" t="n"/>
       <c r="BK87" s="26" t="n">
-        <v>-170</v>
+        <v>104</v>
       </c>
       <c r="BL87" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.04</v>
       </c>
       <c r="BM87" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.490196</v>
       </c>
       <c r="BN87" s="28" t="n"/>
       <c r="BO87" s="28" t="n"/>
@@ -25855,29 +25897,29 @@
       <c r="CR87" s="24" t="n"/>
       <c r="CS87" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
         <is>
-          <t>96772a5ab79f472c</t>
+          <t>8df916fc7b0b4ee3</t>
         </is>
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:55:50.543648Z</t>
+          <t>2026-08-05T21:01:56.767307Z</t>
         </is>
       </c>
       <c r="C88" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:00Z</t>
+          <t>2026-08-05T22:00Z</t>
         </is>
       </c>
       <c r="D88" s="24" t="inlineStr">
         <is>
-          <t>401886451</t>
+          <t>401841460</t>
         </is>
       </c>
       <c r="E88" s="24" t="inlineStr">
@@ -25887,12 +25929,12 @@
       </c>
       <c r="F88" s="24" t="inlineStr">
         <is>
-          <t>Paris Saint-Germain</t>
+          <t>Estudiantes de La Plata</t>
         </is>
       </c>
       <c r="G88" s="24" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="H88" s="24" t="inlineStr">
@@ -25902,7 +25944,7 @@
       </c>
       <c r="I88" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J88" s="25" t="n"/>
@@ -25912,51 +25954,65 @@
         </is>
       </c>
       <c r="L88" s="26" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="M88" s="27" t="n">
-        <v>2</v>
+        <v>1.925926</v>
       </c>
       <c r="N88" s="28" t="n">
-        <v>0.5</v>
+        <v>0.519231</v>
       </c>
       <c r="O88" s="28" t="n">
-        <v>0.526434</v>
+        <v>0.500109</v>
       </c>
       <c r="P88" s="28" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="Q88" s="28" t="n">
-        <v>0.026434</v>
+        <v>-0.019122</v>
       </c>
       <c r="R88" s="26" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S88" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U88" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V88" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W88" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T88" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U88" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V88" s="24" t="n"/>
-      <c r="W88" s="26" t="n"/>
-      <c r="X88" s="26" t="n"/>
       <c r="Y88" s="25" t="n"/>
       <c r="Z88" s="26" t="n"/>
       <c r="AA88" s="28" t="n"/>
       <c r="AB88" s="28" t="n"/>
-      <c r="AC88" s="30" t="n"/>
-      <c r="AD88" s="24" t="n"/>
+      <c r="AC88" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:48.578143Z</t>
+        </is>
+      </c>
       <c r="AE88" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.11 (home) / 1.81 (away) from EWMA attack/defense strengths. Executable ask 0.5000 (atc-clbf-mal-psg-2026-08-05-psg).</t>
+          <t>Poisson-DC rates 1.66 (home) / 1.07 (away) from EWMA attack/defense strengths. Executable ask 0.5200 (atc-lpa-boc-est-2026-08-05-boc).</t>
         </is>
       </c>
       <c r="AF88" s="31" t="inlineStr">
@@ -25992,37 +26048,37 @@
       </c>
       <c r="AO88" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP88" s="24" t="inlineStr">
         <is>
-          <t>Paris Saint-Germain</t>
+          <t>Estudiantes de La Plata</t>
         </is>
       </c>
       <c r="AQ88" s="24" t="inlineStr">
         <is>
-          <t>Paris Saint-Germain</t>
+          <t>Estudiantes de La Plata</t>
         </is>
       </c>
       <c r="AR88" s="24" t="inlineStr">
         <is>
-          <t>Paris Saint-Germain</t>
+          <t>Estudiantes de La Plata</t>
         </is>
       </c>
       <c r="AS88" s="24" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AT88" s="24" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AU88" s="24" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AV88" s="24" t="n"/>
@@ -26075,7 +26131,7 @@
       </c>
       <c r="BH88" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:37.762719Z</t>
+          <t>2026-08-05T21:00:53.073019Z</t>
         </is>
       </c>
       <c r="BI88" s="24" t="inlineStr">
@@ -26085,13 +26141,13 @@
       </c>
       <c r="BJ88" s="25" t="n"/>
       <c r="BK88" s="26" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="BL88" s="27" t="n">
-        <v>2</v>
+        <v>1.925926</v>
       </c>
       <c r="BM88" s="28" t="n">
-        <v>0.5</v>
+        <v>0.519231</v>
       </c>
       <c r="BN88" s="28" t="n"/>
       <c r="BO88" s="28" t="n"/>
@@ -26126,6 +26182,1931 @@
       <c r="CR88" s="24" t="n"/>
       <c r="CS88" s="24" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>e7d7caec12d04e99</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:01:56.767307Z</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00Z</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>401843990</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima (Jujuy)</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J89" s="25" t="n"/>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L89" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M89" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N89" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O89" s="28" t="n">
+        <v>0.440521</v>
+      </c>
+      <c r="P89" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q89" s="28" t="n">
+        <v>-0.020308</v>
+      </c>
+      <c r="R89" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U89" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V89" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W89" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y89" s="25" t="n"/>
+      <c r="Z89" s="26" t="n"/>
+      <c r="AA89" s="28" t="n"/>
+      <c r="AB89" s="28" t="n"/>
+      <c r="AC89" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:26:38.820063Z</t>
+        </is>
+      </c>
+      <c r="AE89" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.46 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-arg2-qui-ge-2026-08-05-qui).</t>
+        </is>
+      </c>
+      <c r="AF89" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG89" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH89" s="24" t="n"/>
+      <c r="AI89" s="31" t="n"/>
+      <c r="AJ89" s="31" t="n"/>
+      <c r="AK89" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL89" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM89" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN89" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO89" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP89" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima (Jujuy)</t>
+        </is>
+      </c>
+      <c r="AQ89" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima (Jujuy)</t>
+        </is>
+      </c>
+      <c r="AR89" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima (Jujuy)</t>
+        </is>
+      </c>
+      <c r="AS89" s="24" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="AT89" s="24" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="AU89" s="24" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="AV89" s="24" t="n"/>
+      <c r="AW89" s="24" t="n"/>
+      <c r="AX89" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY89" s="24" t="n"/>
+      <c r="AZ89" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA89" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB89" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC89" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD89" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE89" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF89" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG89" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH89" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:53.307981Z</t>
+        </is>
+      </c>
+      <c r="BI89" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ89" s="25" t="n"/>
+      <c r="BK89" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL89" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM89" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN89" s="28" t="n"/>
+      <c r="BO89" s="28" t="n"/>
+      <c r="BP89" s="25" t="n"/>
+      <c r="BQ89" s="27" t="n"/>
+      <c r="BR89" s="28" t="n"/>
+      <c r="BS89" s="28" t="n"/>
+      <c r="BT89" s="28" t="n"/>
+      <c r="BU89" s="25" t="n"/>
+      <c r="BV89" s="29" t="n"/>
+      <c r="BW89" s="24" t="n"/>
+      <c r="BX89" s="30" t="n"/>
+      <c r="BY89" s="27" t="n"/>
+      <c r="BZ89" s="24" t="n"/>
+      <c r="CA89" s="31" t="n"/>
+      <c r="CB89" s="24" t="n"/>
+      <c r="CC89" s="24" t="n"/>
+      <c r="CD89" s="24" t="n"/>
+      <c r="CE89" s="24" t="n"/>
+      <c r="CF89" s="24" t="n"/>
+      <c r="CG89" s="24" t="n"/>
+      <c r="CH89" s="24" t="n"/>
+      <c r="CI89" s="24" t="n"/>
+      <c r="CJ89" s="24" t="n"/>
+      <c r="CK89" s="24" t="n"/>
+      <c r="CL89" s="24" t="n"/>
+      <c r="CM89" s="24" t="n"/>
+      <c r="CN89" s="24" t="n"/>
+      <c r="CO89" s="24" t="n"/>
+      <c r="CP89" s="24" t="n"/>
+      <c r="CQ89" s="24" t="n"/>
+      <c r="CR89" s="24" t="n"/>
+      <c r="CS89" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>6d8a9fdda4384935</t>
+        </is>
+      </c>
+      <c r="B90" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:10:39.169965Z</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:00Z</t>
+        </is>
+      </c>
+      <c r="D90" s="24" t="inlineStr">
+        <is>
+          <t>401867952</t>
+        </is>
+      </c>
+      <c r="E90" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F90" s="24" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="G90" s="24" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="H90" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I90" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J90" s="25" t="n"/>
+      <c r="K90" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L90" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M90" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N90" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O90" s="28" t="n">
+        <v>0.784326</v>
+      </c>
+      <c r="P90" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q90" s="28" t="n">
+        <v>0.265095</v>
+      </c>
+      <c r="R90" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S90" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T90" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U90" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V90" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W90" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X90" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y90" s="25" t="n"/>
+      <c r="Z90" s="26" t="n"/>
+      <c r="AA90" s="28" t="n"/>
+      <c r="AB90" s="28" t="n"/>
+      <c r="AC90" s="30" t="n">
+        <v>1.8519</v>
+      </c>
+      <c r="AD90" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:18:25.790098Z</t>
+        </is>
+      </c>
+      <c r="AE90" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 3.72 (home) / 1.43 (away) from EWMA attack/defense strengths. Executable ask 0.5200 (atc-clbf-bmu-avl-2026-08-07-bmu).</t>
+        </is>
+      </c>
+      <c r="AF90" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG90" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH90" s="24" t="n"/>
+      <c r="AI90" s="31" t="n"/>
+      <c r="AJ90" s="31" t="n"/>
+      <c r="AK90" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL90" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM90" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN90" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO90" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP90" s="24" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="AQ90" s="24" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="AR90" s="24" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="AS90" s="24" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="AT90" s="24" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="AU90" s="24" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="AV90" s="24" t="n"/>
+      <c r="AW90" s="24" t="n"/>
+      <c r="AX90" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY90" s="24" t="n"/>
+      <c r="AZ90" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA90" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB90" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC90" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD90" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE90" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF90" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG90" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH90" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:46.980092Z</t>
+        </is>
+      </c>
+      <c r="BI90" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ90" s="25" t="n"/>
+      <c r="BK90" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL90" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM90" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN90" s="28" t="n"/>
+      <c r="BO90" s="28" t="n"/>
+      <c r="BP90" s="25" t="n"/>
+      <c r="BQ90" s="27" t="n"/>
+      <c r="BR90" s="28" t="n"/>
+      <c r="BS90" s="28" t="n"/>
+      <c r="BT90" s="28" t="n"/>
+      <c r="BU90" s="25" t="n"/>
+      <c r="BV90" s="29" t="n"/>
+      <c r="BW90" s="24" t="n"/>
+      <c r="BX90" s="30" t="n"/>
+      <c r="BY90" s="27" t="n"/>
+      <c r="BZ90" s="24" t="n"/>
+      <c r="CA90" s="31" t="n"/>
+      <c r="CB90" s="24" t="n"/>
+      <c r="CC90" s="24" t="n"/>
+      <c r="CD90" s="24" t="n"/>
+      <c r="CE90" s="24" t="n"/>
+      <c r="CF90" s="24" t="n"/>
+      <c r="CG90" s="24" t="n"/>
+      <c r="CH90" s="24" t="n"/>
+      <c r="CI90" s="24" t="n"/>
+      <c r="CJ90" s="24" t="n"/>
+      <c r="CK90" s="24" t="n"/>
+      <c r="CL90" s="24" t="n"/>
+      <c r="CM90" s="24" t="n"/>
+      <c r="CN90" s="24" t="n"/>
+      <c r="CO90" s="24" t="n"/>
+      <c r="CP90" s="24" t="n"/>
+      <c r="CQ90" s="24" t="n"/>
+      <c r="CR90" s="24" t="n"/>
+      <c r="CS90" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>5afdf13751d34ca0</t>
+        </is>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:23.257923Z</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T23:30Z</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>401860269</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J91" s="25" t="n"/>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L91" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M91" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N91" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O91" s="28" t="n">
+        <v>0.483295</v>
+      </c>
+      <c r="P91" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q91" s="28" t="n">
+        <v>-0.216405</v>
+      </c>
+      <c r="R91" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U91" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V91" s="24" t="n"/>
+      <c r="W91" s="26" t="n"/>
+      <c r="X91" s="26" t="n"/>
+      <c r="Y91" s="25" t="n"/>
+      <c r="Z91" s="26" t="n"/>
+      <c r="AA91" s="28" t="n"/>
+      <c r="AB91" s="28" t="n"/>
+      <c r="AC91" s="30" t="n"/>
+      <c r="AD91" s="24" t="n"/>
+      <c r="AE91" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.72 (home) / 1.20 (away) from EWMA attack/defense strengths. Executable ask 0.7000 (atc-brb-csc-pop-2026-08-07-csc).</t>
+        </is>
+      </c>
+      <c r="AF91" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG91" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH91" s="24" t="n"/>
+      <c r="AI91" s="31" t="n"/>
+      <c r="AJ91" s="31" t="n"/>
+      <c r="AK91" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL91" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM91" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN91" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO91" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP91" s="24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="AQ91" s="24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="AR91" s="24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="AS91" s="24" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="AT91" s="24" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="AU91" s="24" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="AV91" s="24" t="n"/>
+      <c r="AW91" s="24" t="n"/>
+      <c r="AX91" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY91" s="24" t="n"/>
+      <c r="AZ91" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA91" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB91" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC91" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD91" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE91" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF91" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG91" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH91" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:40.774058Z</t>
+        </is>
+      </c>
+      <c r="BI91" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ91" s="25" t="n"/>
+      <c r="BK91" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL91" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM91" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN91" s="28" t="n"/>
+      <c r="BO91" s="28" t="n"/>
+      <c r="BP91" s="25" t="n"/>
+      <c r="BQ91" s="27" t="n"/>
+      <c r="BR91" s="28" t="n"/>
+      <c r="BS91" s="28" t="n"/>
+      <c r="BT91" s="28" t="n"/>
+      <c r="BU91" s="25" t="n"/>
+      <c r="BV91" s="29" t="n"/>
+      <c r="BW91" s="24" t="n"/>
+      <c r="BX91" s="30" t="n"/>
+      <c r="BY91" s="27" t="n"/>
+      <c r="BZ91" s="24" t="n"/>
+      <c r="CA91" s="31" t="n"/>
+      <c r="CB91" s="24" t="n"/>
+      <c r="CC91" s="24" t="n"/>
+      <c r="CD91" s="24" t="n"/>
+      <c r="CE91" s="24" t="n"/>
+      <c r="CF91" s="24" t="n"/>
+      <c r="CG91" s="24" t="n"/>
+      <c r="CH91" s="24" t="n"/>
+      <c r="CI91" s="24" t="n"/>
+      <c r="CJ91" s="24" t="n"/>
+      <c r="CK91" s="24" t="n"/>
+      <c r="CL91" s="24" t="n"/>
+      <c r="CM91" s="24" t="n"/>
+      <c r="CN91" s="24" t="n"/>
+      <c r="CO91" s="24" t="n"/>
+      <c r="CP91" s="24" t="n"/>
+      <c r="CQ91" s="24" t="n"/>
+      <c r="CR91" s="24" t="n"/>
+      <c r="CS91" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="24" t="inlineStr">
+        <is>
+          <t>8cd2362b4142467d</t>
+        </is>
+      </c>
+      <c r="B92" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:23.257923Z</t>
+        </is>
+      </c>
+      <c r="C92" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T22:30Z</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="inlineStr">
+        <is>
+          <t>401841491</t>
+        </is>
+      </c>
+      <c r="E92" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F92" s="24" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="H92" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I92" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J92" s="25" t="n"/>
+      <c r="K92" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L92" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M92" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N92" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O92" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P92" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q92" s="28" t="n">
+        <v>-0.194215</v>
+      </c>
+      <c r="R92" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U92" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V92" s="24" t="n"/>
+      <c r="W92" s="26" t="n"/>
+      <c r="X92" s="26" t="n"/>
+      <c r="Y92" s="25" t="n"/>
+      <c r="Z92" s="26" t="n"/>
+      <c r="AA92" s="28" t="n"/>
+      <c r="AB92" s="28" t="n"/>
+      <c r="AC92" s="30" t="n"/>
+      <c r="AD92" s="24" t="n"/>
+      <c r="AE92" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6500 (atc-lpa-ros-ald-2026-08-07-ros).</t>
+        </is>
+      </c>
+      <c r="AF92" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG92" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH92" s="24" t="n"/>
+      <c r="AI92" s="31" t="n"/>
+      <c r="AJ92" s="31" t="n"/>
+      <c r="AK92" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL92" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM92" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN92" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO92" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP92" s="24" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="AQ92" s="24" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="AR92" s="24" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="AS92" s="24" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="AT92" s="24" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="AU92" s="24" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="AV92" s="24" t="n"/>
+      <c r="AW92" s="24" t="n"/>
+      <c r="AX92" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY92" s="24" t="n"/>
+      <c r="AZ92" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA92" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB92" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC92" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD92" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE92" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF92" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG92" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH92" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:40.891696Z</t>
+        </is>
+      </c>
+      <c r="BI92" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ92" s="25" t="n"/>
+      <c r="BK92" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL92" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM92" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN92" s="28" t="n"/>
+      <c r="BO92" s="28" t="n"/>
+      <c r="BP92" s="25" t="n"/>
+      <c r="BQ92" s="27" t="n"/>
+      <c r="BR92" s="28" t="n"/>
+      <c r="BS92" s="28" t="n"/>
+      <c r="BT92" s="28" t="n"/>
+      <c r="BU92" s="25" t="n"/>
+      <c r="BV92" s="29" t="n"/>
+      <c r="BW92" s="24" t="n"/>
+      <c r="BX92" s="30" t="n"/>
+      <c r="BY92" s="27" t="n"/>
+      <c r="BZ92" s="24" t="n"/>
+      <c r="CA92" s="31" t="n"/>
+      <c r="CB92" s="24" t="n"/>
+      <c r="CC92" s="24" t="n"/>
+      <c r="CD92" s="24" t="n"/>
+      <c r="CE92" s="24" t="n"/>
+      <c r="CF92" s="24" t="n"/>
+      <c r="CG92" s="24" t="n"/>
+      <c r="CH92" s="24" t="n"/>
+      <c r="CI92" s="24" t="n"/>
+      <c r="CJ92" s="24" t="n"/>
+      <c r="CK92" s="24" t="n"/>
+      <c r="CL92" s="24" t="n"/>
+      <c r="CM92" s="24" t="n"/>
+      <c r="CN92" s="24" t="n"/>
+      <c r="CO92" s="24" t="n"/>
+      <c r="CP92" s="24" t="n"/>
+      <c r="CQ92" s="24" t="n"/>
+      <c r="CR92" s="24" t="n"/>
+      <c r="CS92" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
+      <c r="A93" s="24" t="inlineStr">
+        <is>
+          <t>d916b99fe3634907</t>
+        </is>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:23.257923Z</t>
+        </is>
+      </c>
+      <c r="C93" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T22:00Z</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>401905201</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F93" s="24" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J93" s="25" t="n"/>
+      <c r="K93" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L93" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M93" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N93" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O93" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P93" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q93" s="28" t="n">
+        <v>0.126102</v>
+      </c>
+      <c r="R93" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U93" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V93" s="24" t="n"/>
+      <c r="W93" s="26" t="n"/>
+      <c r="X93" s="26" t="n"/>
+      <c r="Y93" s="25" t="n"/>
+      <c r="Z93" s="26" t="n"/>
+      <c r="AA93" s="28" t="n"/>
+      <c r="AB93" s="28" t="n"/>
+      <c r="AC93" s="30" t="n"/>
+      <c r="AD93" s="24" t="n"/>
+      <c r="AE93" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-uru1-cla-juv-2026-08-07-cla).</t>
+        </is>
+      </c>
+      <c r="AF93" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG93" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH93" s="24" t="n"/>
+      <c r="AI93" s="31" t="n"/>
+      <c r="AJ93" s="31" t="n"/>
+      <c r="AK93" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL93" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM93" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN93" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO93" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP93" s="24" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="AQ93" s="24" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="AR93" s="24" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="AS93" s="24" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="AT93" s="24" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="AU93" s="24" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="AV93" s="24" t="n"/>
+      <c r="AW93" s="24" t="n"/>
+      <c r="AX93" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY93" s="24" t="n"/>
+      <c r="AZ93" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA93" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB93" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC93" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD93" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE93" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF93" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG93" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH93" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:41.371011Z</t>
+        </is>
+      </c>
+      <c r="BI93" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ93" s="25" t="n"/>
+      <c r="BK93" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL93" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM93" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN93" s="28" t="n"/>
+      <c r="BO93" s="28" t="n"/>
+      <c r="BP93" s="25" t="n"/>
+      <c r="BQ93" s="27" t="n"/>
+      <c r="BR93" s="28" t="n"/>
+      <c r="BS93" s="28" t="n"/>
+      <c r="BT93" s="28" t="n"/>
+      <c r="BU93" s="25" t="n"/>
+      <c r="BV93" s="29" t="n"/>
+      <c r="BW93" s="24" t="n"/>
+      <c r="BX93" s="30" t="n"/>
+      <c r="BY93" s="27" t="n"/>
+      <c r="BZ93" s="24" t="n"/>
+      <c r="CA93" s="31" t="n"/>
+      <c r="CB93" s="24" t="n"/>
+      <c r="CC93" s="24" t="n"/>
+      <c r="CD93" s="24" t="n"/>
+      <c r="CE93" s="24" t="n"/>
+      <c r="CF93" s="24" t="n"/>
+      <c r="CG93" s="24" t="n"/>
+      <c r="CH93" s="24" t="n"/>
+      <c r="CI93" s="24" t="n"/>
+      <c r="CJ93" s="24" t="n"/>
+      <c r="CK93" s="24" t="n"/>
+      <c r="CL93" s="24" t="n"/>
+      <c r="CM93" s="24" t="n"/>
+      <c r="CN93" s="24" t="n"/>
+      <c r="CO93" s="24" t="n"/>
+      <c r="CP93" s="24" t="n"/>
+      <c r="CQ93" s="24" t="n"/>
+      <c r="CR93" s="24" t="n"/>
+      <c r="CS93" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1">
+      <c r="A94" s="24" t="inlineStr">
+        <is>
+          <t>871ee6db0f564f4f</t>
+        </is>
+      </c>
+      <c r="B94" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:23.257923Z</t>
+        </is>
+      </c>
+      <c r="C94" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:15Z</t>
+        </is>
+      </c>
+      <c r="D94" s="24" t="inlineStr">
+        <is>
+          <t>401886111</t>
+        </is>
+      </c>
+      <c r="E94" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F94" s="24" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="G94" s="24" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="H94" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I94" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J94" s="25" t="n"/>
+      <c r="K94" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L94" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M94" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N94" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O94" s="28" t="n">
+        <v>0.394611</v>
+      </c>
+      <c r="P94" s="28" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q94" s="28" t="n">
+        <v>0.003986</v>
+      </c>
+      <c r="R94" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U94" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V94" s="24" t="n"/>
+      <c r="W94" s="26" t="n"/>
+      <c r="X94" s="26" t="n"/>
+      <c r="Y94" s="25" t="n"/>
+      <c r="Z94" s="26" t="n"/>
+      <c r="AA94" s="28" t="n"/>
+      <c r="AB94" s="28" t="n"/>
+      <c r="AC94" s="30" t="n"/>
+      <c r="AD94" s="24" t="n"/>
+      <c r="AE94" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.66 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (atc-pl1-cou-gar-2026-08-07-cou).</t>
+        </is>
+      </c>
+      <c r="AF94" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG94" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH94" s="24" t="n"/>
+      <c r="AI94" s="31" t="n"/>
+      <c r="AJ94" s="31" t="n"/>
+      <c r="AK94" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL94" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM94" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN94" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO94" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP94" s="24" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="AQ94" s="24" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="AR94" s="24" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="AS94" s="24" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="AT94" s="24" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="AU94" s="24" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="AV94" s="24" t="n"/>
+      <c r="AW94" s="24" t="n"/>
+      <c r="AX94" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY94" s="24" t="n"/>
+      <c r="AZ94" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA94" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB94" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC94" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD94" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE94" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF94" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG94" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH94" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:41.859430Z</t>
+        </is>
+      </c>
+      <c r="BI94" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ94" s="25" t="n"/>
+      <c r="BK94" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL94" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM94" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN94" s="28" t="n"/>
+      <c r="BO94" s="28" t="n"/>
+      <c r="BP94" s="25" t="n"/>
+      <c r="BQ94" s="27" t="n"/>
+      <c r="BR94" s="28" t="n"/>
+      <c r="BS94" s="28" t="n"/>
+      <c r="BT94" s="28" t="n"/>
+      <c r="BU94" s="25" t="n"/>
+      <c r="BV94" s="29" t="n"/>
+      <c r="BW94" s="24" t="n"/>
+      <c r="BX94" s="30" t="n"/>
+      <c r="BY94" s="27" t="n"/>
+      <c r="BZ94" s="24" t="n"/>
+      <c r="CA94" s="31" t="n"/>
+      <c r="CB94" s="24" t="n"/>
+      <c r="CC94" s="24" t="n"/>
+      <c r="CD94" s="24" t="n"/>
+      <c r="CE94" s="24" t="n"/>
+      <c r="CF94" s="24" t="n"/>
+      <c r="CG94" s="24" t="n"/>
+      <c r="CH94" s="24" t="n"/>
+      <c r="CI94" s="24" t="n"/>
+      <c r="CJ94" s="24" t="n"/>
+      <c r="CK94" s="24" t="n"/>
+      <c r="CL94" s="24" t="n"/>
+      <c r="CM94" s="24" t="n"/>
+      <c r="CN94" s="24" t="n"/>
+      <c r="CO94" s="24" t="n"/>
+      <c r="CP94" s="24" t="n"/>
+      <c r="CQ94" s="24" t="n"/>
+      <c r="CR94" s="24" t="n"/>
+      <c r="CS94" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="A95" s="24" t="inlineStr">
+        <is>
+          <t>ef7d1959c9ed435a</t>
+        </is>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:23.257923Z</t>
+        </is>
+      </c>
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:45Z</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>401906279</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F95" s="24" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J95" s="25" t="n"/>
+      <c r="K95" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L95" s="26" t="n">
+        <v>456</v>
+      </c>
+      <c r="M95" s="27" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="N95" s="28" t="n">
+        <v>0.179856</v>
+      </c>
+      <c r="O95" s="28" t="n">
+        <v>0.5644479999999999</v>
+      </c>
+      <c r="P95" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q95" s="28" t="n">
+        <v>0.384592</v>
+      </c>
+      <c r="R95" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S95" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U95" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V95" s="24" t="n"/>
+      <c r="W95" s="26" t="n"/>
+      <c r="X95" s="26" t="n"/>
+      <c r="Y95" s="25" t="n"/>
+      <c r="Z95" s="26" t="n"/>
+      <c r="AA95" s="28" t="n"/>
+      <c r="AB95" s="28" t="n"/>
+      <c r="AC95" s="30" t="n"/>
+      <c r="AD95" s="24" t="n"/>
+      <c r="AE95" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 0.86 (home) / 1.71 (away) from EWMA attack/defense strengths. Executable ask 0.1800 (atc-clbf-mon-pad-2026-08-07-pad).</t>
+        </is>
+      </c>
+      <c r="AF95" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG95" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH95" s="24" t="n"/>
+      <c r="AI95" s="31" t="n"/>
+      <c r="AJ95" s="31" t="n"/>
+      <c r="AK95" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL95" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM95" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN95" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO95" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP95" s="24" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="AQ95" s="24" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="AR95" s="24" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="AS95" s="24" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="AT95" s="24" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="AU95" s="24" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="AV95" s="24" t="n"/>
+      <c r="AW95" s="24" t="n"/>
+      <c r="AX95" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY95" s="24" t="n"/>
+      <c r="AZ95" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA95" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB95" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC95" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD95" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE95" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF95" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG95" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH95" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:42.028691Z</t>
+        </is>
+      </c>
+      <c r="BI95" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ95" s="25" t="n"/>
+      <c r="BK95" s="26" t="n">
+        <v>456</v>
+      </c>
+      <c r="BL95" s="27" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="BM95" s="28" t="n">
+        <v>0.179856</v>
+      </c>
+      <c r="BN95" s="28" t="n"/>
+      <c r="BO95" s="28" t="n"/>
+      <c r="BP95" s="25" t="n"/>
+      <c r="BQ95" s="27" t="n"/>
+      <c r="BR95" s="28" t="n"/>
+      <c r="BS95" s="28" t="n"/>
+      <c r="BT95" s="28" t="n"/>
+      <c r="BU95" s="25" t="n"/>
+      <c r="BV95" s="29" t="n"/>
+      <c r="BW95" s="24" t="n"/>
+      <c r="BX95" s="30" t="n"/>
+      <c r="BY95" s="27" t="n"/>
+      <c r="BZ95" s="24" t="n"/>
+      <c r="CA95" s="31" t="n"/>
+      <c r="CB95" s="24" t="n"/>
+      <c r="CC95" s="24" t="n"/>
+      <c r="CD95" s="24" t="n"/>
+      <c r="CE95" s="24" t="n"/>
+      <c r="CF95" s="24" t="n"/>
+      <c r="CG95" s="24" t="n"/>
+      <c r="CH95" s="24" t="n"/>
+      <c r="CI95" s="24" t="n"/>
+      <c r="CJ95" s="24" t="n"/>
+      <c r="CK95" s="24" t="n"/>
+      <c r="CL95" s="24" t="n"/>
+      <c r="CM95" s="24" t="n"/>
+      <c r="CN95" s="24" t="n"/>
+      <c r="CO95" s="24" t="n"/>
+      <c r="CP95" s="24" t="n"/>
+      <c r="CQ95" s="24" t="n"/>
+      <c r="CR95" s="24" t="n"/>
+      <c r="CS95" s="24" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>

--- a/data/flat/soccer.xlsx
+++ b/data/flat/soccer.xlsx
@@ -26759,12 +26759,12 @@
     <row r="91" ht="36" customHeight="1">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t>5afdf13751d34ca0</t>
+          <t>f058390f4b004de1</t>
         </is>
       </c>
       <c r="B91" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:23.257923Z</t>
+          <t>2026-08-07T18:30:33.836209Z</t>
         </is>
       </c>
       <c r="C91" s="24" t="inlineStr">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="BH91" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:40.774058Z</t>
+          <t>2026-08-07T18:28:04.155625Z</t>
         </is>
       </c>
       <c r="BI91" s="24" t="inlineStr">
@@ -27030,12 +27030,12 @@
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="24" t="inlineStr">
         <is>
-          <t>8cd2362b4142467d</t>
+          <t>09814b91eb264833</t>
         </is>
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:23.257923Z</t>
+          <t>2026-08-07T18:30:33.836209Z</t>
         </is>
       </c>
       <c r="C92" s="24" t="inlineStr">
@@ -27080,13 +27080,13 @@
         </is>
       </c>
       <c r="L92" s="26" t="n">
-        <v>-186</v>
+        <v>-194</v>
       </c>
       <c r="M92" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.515464</v>
       </c>
       <c r="N92" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.659864</v>
       </c>
       <c r="O92" s="28" t="n">
         <v>0.456135</v>
@@ -27095,7 +27095,7 @@
         <v>0.2</v>
       </c>
       <c r="Q92" s="28" t="n">
-        <v>-0.194215</v>
+        <v>-0.203729</v>
       </c>
       <c r="R92" s="26" t="n">
         <v>0</v>
@@ -27124,7 +27124,7 @@
       <c r="AD92" s="24" t="n"/>
       <c r="AE92" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6500 (atc-lpa-ros-ald-2026-08-07-ros).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6600 (atc-lpa-ros-ald-2026-08-07-ros).</t>
         </is>
       </c>
       <c r="AF92" s="31" t="inlineStr">
@@ -27243,7 +27243,7 @@
       </c>
       <c r="BH92" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:40.891696Z</t>
+          <t>2026-08-07T18:28:04.333422Z</t>
         </is>
       </c>
       <c r="BI92" s="24" t="inlineStr">
@@ -27253,13 +27253,13 @@
       </c>
       <c r="BJ92" s="25" t="n"/>
       <c r="BK92" s="26" t="n">
-        <v>-186</v>
+        <v>-194</v>
       </c>
       <c r="BL92" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.515464</v>
       </c>
       <c r="BM92" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.659864</v>
       </c>
       <c r="BN92" s="28" t="n"/>
       <c r="BO92" s="28" t="n"/>
@@ -27301,12 +27301,12 @@
     <row r="93" ht="36" customHeight="1">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>d916b99fe3634907</t>
+          <t>5568763dc4a944db</t>
         </is>
       </c>
       <c r="B93" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:23.257923Z</t>
+          <t>2026-08-07T18:30:33.836209Z</t>
         </is>
       </c>
       <c r="C93" s="24" t="inlineStr">
@@ -27351,13 +27351,13 @@
         </is>
       </c>
       <c r="L93" s="26" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="M93" s="27" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="N93" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.340136</v>
       </c>
       <c r="O93" s="28" t="n">
         <v>0.456135</v>
@@ -27366,7 +27366,7 @@
         <v>0.2</v>
       </c>
       <c r="Q93" s="28" t="n">
-        <v>0.126102</v>
+        <v>0.115999</v>
       </c>
       <c r="R93" s="26" t="n">
         <v>0</v>
@@ -27395,7 +27395,7 @@
       <c r="AD93" s="24" t="n"/>
       <c r="AE93" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-uru1-cla-juv-2026-08-07-cla).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3400 (atc-uru1-cla-juv-2026-08-07-cla).</t>
         </is>
       </c>
       <c r="AF93" s="31" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="BH93" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:41.371011Z</t>
+          <t>2026-08-07T18:28:04.740187Z</t>
         </is>
       </c>
       <c r="BI93" s="24" t="inlineStr">
@@ -27524,13 +27524,13 @@
       </c>
       <c r="BJ93" s="25" t="n"/>
       <c r="BK93" s="26" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="BL93" s="27" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="BM93" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.340136</v>
       </c>
       <c r="BN93" s="28" t="n"/>
       <c r="BO93" s="28" t="n"/>
@@ -27572,12 +27572,12 @@
     <row r="94" ht="36" customHeight="1">
       <c r="A94" s="24" t="inlineStr">
         <is>
-          <t>871ee6db0f564f4f</t>
+          <t>ec9fbb53d3bd434e</t>
         </is>
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:23.257923Z</t>
+          <t>2026-08-07T18:30:33.836209Z</t>
         </is>
       </c>
       <c r="C94" s="24" t="inlineStr">
@@ -27622,13 +27622,13 @@
         </is>
       </c>
       <c r="L94" s="26" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="M94" s="27" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="N94" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.380228</v>
       </c>
       <c r="O94" s="28" t="n">
         <v>0.394611</v>
@@ -27637,7 +27637,7 @@
         <v>0.19</v>
       </c>
       <c r="Q94" s="28" t="n">
-        <v>0.003986</v>
+        <v>0.014383</v>
       </c>
       <c r="R94" s="26" t="n">
         <v>0</v>
@@ -27666,7 +27666,7 @@
       <c r="AD94" s="24" t="n"/>
       <c r="AE94" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.66 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (atc-pl1-cou-gar-2026-08-07-cou).</t>
+          <t>Poisson-DC rates 1.66 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3800 (atc-pl1-cou-gar-2026-08-07-cou).</t>
         </is>
       </c>
       <c r="AF94" s="31" t="inlineStr">
@@ -27785,7 +27785,7 @@
       </c>
       <c r="BH94" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:41.859430Z</t>
+          <t>2026-08-07T18:28:05.240611Z</t>
         </is>
       </c>
       <c r="BI94" s="24" t="inlineStr">
@@ -27795,13 +27795,13 @@
       </c>
       <c r="BJ94" s="25" t="n"/>
       <c r="BK94" s="26" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="BL94" s="27" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BM94" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.380228</v>
       </c>
       <c r="BN94" s="28" t="n"/>
       <c r="BO94" s="28" t="n"/>
@@ -27843,12 +27843,12 @@
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>ef7d1959c9ed435a</t>
+          <t>65cbf0fd53194669</t>
         </is>
       </c>
       <c r="B95" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:23.257923Z</t>
+          <t>2026-08-07T18:30:33.836209Z</t>
         </is>
       </c>
       <c r="C95" s="24" t="inlineStr">
@@ -27893,13 +27893,13 @@
         </is>
       </c>
       <c r="L95" s="26" t="n">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="M95" s="27" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="N95" s="28" t="n">
-        <v>0.179856</v>
+        <v>0.190114</v>
       </c>
       <c r="O95" s="28" t="n">
         <v>0.5644479999999999</v>
@@ -27908,7 +27908,7 @@
         <v>0.2</v>
       </c>
       <c r="Q95" s="28" t="n">
-        <v>0.384592</v>
+        <v>0.374334</v>
       </c>
       <c r="R95" s="26" t="n">
         <v>100</v>
@@ -27937,7 +27937,7 @@
       <c r="AD95" s="24" t="n"/>
       <c r="AE95" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 0.86 (home) / 1.71 (away) from EWMA attack/defense strengths. Executable ask 0.1800 (atc-clbf-mon-pad-2026-08-07-pad).</t>
+          <t>Poisson-DC rates 0.86 (home) / 1.71 (away) from EWMA attack/defense strengths. Executable ask 0.1900 (atc-clbf-mon-pad-2026-08-07-pad).</t>
         </is>
       </c>
       <c r="AF95" s="31" t="inlineStr">
@@ -28056,7 +28056,7 @@
       </c>
       <c r="BH95" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:42.028691Z</t>
+          <t>2026-08-07T18:28:05.312057Z</t>
         </is>
       </c>
       <c r="BI95" s="24" t="inlineStr">
@@ -28066,13 +28066,13 @@
       </c>
       <c r="BJ95" s="25" t="n"/>
       <c r="BK95" s="26" t="n">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="BL95" s="27" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BM95" s="28" t="n">
-        <v>0.179856</v>
+        <v>0.190114</v>
       </c>
       <c r="BN95" s="28" t="n"/>
       <c r="BO95" s="28" t="n"/>

--- a/data/flat/soccer.xlsx
+++ b/data/flat/soccer.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS142" headerRowCount="1">
-  <autoFilter ref="A1:CS142"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS146" headerRowCount="1">
+  <autoFilter ref="A1:CS146"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$142)</f>
+        <f>COUNTA('Picks'!$A$2:$A$146)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$142,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$146,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$142,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$146,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$142,"settled",'Picks'!$V$2:$V$142,"win")+COUNTIFS('Picks'!$U$2:$U$142,"settled",'Picks'!$V$2:$V$142,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"win")+COUNTIFS('Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$142,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$146,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$142,"&gt;0",'Picks'!$V$2:$V$142,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$142,"&gt;0",'Picks'!$V$2:$V$142,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$142,"&gt;0",'Picks'!$V$2:$V$142,"win")/(COUNTIFS('Picks'!$BX$2:$BX$142,"&gt;0",'Picks'!$V$2:$V$142,"win")+COUNTIFS('Picks'!$BX$2:$BX$142,"&gt;0",'Picks'!$V$2:$V$142,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"win")/(COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"win")+COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$142)/SUM('Picks'!$BX$2:$BX$142),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$146)/SUM('Picks'!$BX$2:$BX$146),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$142)</f>
+        <f>SUM('Picks'!$BY$2:$BY$146)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$142,"&lt;&gt;",'Picks'!$AB$2:$AB$142),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$146,"&lt;&gt;",'Picks'!$AB$2:$AB$146),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$142,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$142,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$146,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$146,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$142,'Picks'!$AM$2:$AM$142,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$146,'Picks'!$AM$2:$AM$146,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$142,$A14,'Picks'!$U$2:$U$142,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$146,$A14,'Picks'!$U$2:$U$146,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$142,$A14,'Picks'!$U$2:$U$142,"settled",'Picks'!$V$2:$V$142,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$146,$A14,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$142,$A14,'Picks'!$U$2:$U$142,"settled",'Picks'!$V$2:$V$142,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$146,$A14,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$142,'Picks'!$H$2:$H$142,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$146,'Picks'!$H$2:$H$146,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$142,'Picks'!$H$2:$H$142,$A14,'Picks'!$U$2:$U$142,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$146,'Picks'!$H$2:$H$146,$A14,'Picks'!$U$2:$U$146,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$142,$A15,'Picks'!$U$2:$U$142,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$146,$A15,'Picks'!$U$2:$U$146,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$142,$A15,'Picks'!$U$2:$U$142,"settled",'Picks'!$V$2:$V$142,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$146,$A15,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$142,$A15,'Picks'!$U$2:$U$142,"settled",'Picks'!$V$2:$V$142,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$146,$A15,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$142,'Picks'!$H$2:$H$142,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$146,'Picks'!$H$2:$H$146,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$142,'Picks'!$H$2:$H$142,$A15,'Picks'!$U$2:$U$142,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$146,'Picks'!$H$2:$H$146,$A15,'Picks'!$U$2:$U$146,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$142,$A16,'Picks'!$U$2:$U$142,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$146,$A16,'Picks'!$U$2:$U$146,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$142,$A16,'Picks'!$U$2:$U$142,"settled",'Picks'!$V$2:$V$142,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$146,$A16,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$142,$A16,'Picks'!$U$2:$U$142,"settled",'Picks'!$V$2:$V$142,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$146,$A16,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$142,'Picks'!$H$2:$H$142,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$146,'Picks'!$H$2:$H$146,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$142,'Picks'!$H$2:$H$142,$A16,'Picks'!$U$2:$U$142,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$146,'Picks'!$H$2:$H$146,$A16,'Picks'!$U$2:$U$146,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS142"/>
+  <dimension ref="A1:CS146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -25120,7 +25120,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" s="24" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
       <c r="AA85" s="28" t="n"/>
       <c r="AB85" s="28" t="n"/>
       <c r="AC85" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD85" s="24" t="inlineStr">
         <is>
@@ -25172,7 +25172,11 @@
       </c>
       <c r="AH85" s="24" t="n"/>
       <c r="AI85" s="31" t="n"/>
-      <c r="AJ85" s="31" t="n"/>
+      <c r="AJ85" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK85" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -25405,7 +25409,7 @@
         <v>4</v>
       </c>
       <c r="S86" s="29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T86" s="24" t="inlineStr">
         <is>
@@ -25433,7 +25437,7 @@
       <c r="AA86" s="28" t="n"/>
       <c r="AB86" s="28" t="n"/>
       <c r="AC86" s="30" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AD86" s="24" t="inlineStr">
         <is>
@@ -25457,7 +25461,11 @@
       </c>
       <c r="AH86" s="24" t="n"/>
       <c r="AI86" s="31" t="n"/>
-      <c r="AJ86" s="31" t="n"/>
+      <c r="AJ86" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK86" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -25690,7 +25698,7 @@
         <v>44</v>
       </c>
       <c r="S87" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" s="24" t="inlineStr">
         <is>
@@ -25718,7 +25726,7 @@
       <c r="AA87" s="28" t="n"/>
       <c r="AB87" s="28" t="n"/>
       <c r="AC87" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD87" s="24" t="inlineStr">
         <is>
@@ -25742,7 +25750,11 @@
       </c>
       <c r="AH87" s="24" t="n"/>
       <c r="AI87" s="31" t="n"/>
-      <c r="AJ87" s="31" t="n"/>
+      <c r="AJ87" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK87" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -25975,7 +25987,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" s="24" t="inlineStr">
         <is>
@@ -26003,7 +26015,7 @@
       <c r="AA88" s="28" t="n"/>
       <c r="AB88" s="28" t="n"/>
       <c r="AC88" s="30" t="n">
-        <v>0</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="AD88" s="24" t="inlineStr">
         <is>
@@ -26027,7 +26039,11 @@
       </c>
       <c r="AH88" s="24" t="n"/>
       <c r="AI88" s="31" t="n"/>
-      <c r="AJ88" s="31" t="n"/>
+      <c r="AJ88" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK88" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -26260,7 +26276,7 @@
         <v>0</v>
       </c>
       <c r="S89" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" s="24" t="inlineStr">
         <is>
@@ -26288,7 +26304,7 @@
       <c r="AA89" s="28" t="n"/>
       <c r="AB89" s="28" t="n"/>
       <c r="AC89" s="30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD89" s="24" t="inlineStr">
         <is>
@@ -26312,7 +26328,11 @@
       </c>
       <c r="AH89" s="24" t="n"/>
       <c r="AI89" s="31" t="n"/>
-      <c r="AJ89" s="31" t="n"/>
+      <c r="AJ89" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK89" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -26830,7 +26850,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" s="24" t="inlineStr">
         <is>
@@ -26858,7 +26878,7 @@
       <c r="AA91" s="28" t="n"/>
       <c r="AB91" s="28" t="n"/>
       <c r="AC91" s="30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD91" s="24" t="inlineStr">
         <is>
@@ -26882,7 +26902,11 @@
       </c>
       <c r="AH91" s="24" t="n"/>
       <c r="AI91" s="31" t="n"/>
-      <c r="AJ91" s="31" t="n"/>
+      <c r="AJ91" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK91" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -27400,7 +27424,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" s="24" t="inlineStr">
         <is>
@@ -27428,7 +27452,7 @@
       <c r="AA93" s="28" t="n"/>
       <c r="AB93" s="28" t="n"/>
       <c r="AC93" s="30" t="n">
-        <v>0</v>
+        <v>0.4695</v>
       </c>
       <c r="AD93" s="24" t="inlineStr">
         <is>
@@ -27452,7 +27476,11 @@
       </c>
       <c r="AH93" s="24" t="n"/>
       <c r="AI93" s="31" t="n"/>
-      <c r="AJ93" s="31" t="n"/>
+      <c r="AJ93" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK93" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -27685,7 +27713,7 @@
         <v>0</v>
       </c>
       <c r="S94" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" s="24" t="inlineStr">
         <is>
@@ -27713,7 +27741,7 @@
       <c r="AA94" s="28" t="n"/>
       <c r="AB94" s="28" t="n"/>
       <c r="AC94" s="30" t="n">
-        <v>0</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="AD94" s="24" t="inlineStr">
         <is>
@@ -27737,7 +27765,11 @@
       </c>
       <c r="AH94" s="24" t="n"/>
       <c r="AI94" s="31" t="n"/>
-      <c r="AJ94" s="31" t="n"/>
+      <c r="AJ94" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK94" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -27970,7 +28002,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" s="24" t="inlineStr">
         <is>
@@ -27998,7 +28030,7 @@
       <c r="AA95" s="28" t="n"/>
       <c r="AB95" s="28" t="n"/>
       <c r="AC95" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD95" s="24" t="inlineStr">
         <is>
@@ -28022,7 +28054,11 @@
       </c>
       <c r="AH95" s="24" t="n"/>
       <c r="AI95" s="31" t="n"/>
-      <c r="AJ95" s="31" t="n"/>
+      <c r="AJ95" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK95" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -28540,7 +28576,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" s="24" t="inlineStr">
         <is>
@@ -28568,7 +28604,7 @@
       <c r="AA97" s="28" t="n"/>
       <c r="AB97" s="28" t="n"/>
       <c r="AC97" s="30" t="n">
-        <v>0</v>
+        <v>0.6944</v>
       </c>
       <c r="AD97" s="24" t="inlineStr">
         <is>
@@ -28592,7 +28628,11 @@
       </c>
       <c r="AH97" s="24" t="n"/>
       <c r="AI97" s="31" t="n"/>
-      <c r="AJ97" s="31" t="n"/>
+      <c r="AJ97" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK97" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -28825,7 +28865,7 @@
         <v>0</v>
       </c>
       <c r="S98" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" s="24" t="inlineStr">
         <is>
@@ -28853,7 +28893,7 @@
       <c r="AA98" s="28" t="n"/>
       <c r="AB98" s="28" t="n"/>
       <c r="AC98" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD98" s="24" t="inlineStr">
         <is>
@@ -28877,7 +28917,11 @@
       </c>
       <c r="AH98" s="24" t="n"/>
       <c r="AI98" s="31" t="n"/>
-      <c r="AJ98" s="31" t="n"/>
+      <c r="AJ98" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK98" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -29110,7 +29154,7 @@
         <v>0</v>
       </c>
       <c r="S99" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" s="24" t="inlineStr">
         <is>
@@ -29138,7 +29182,7 @@
       <c r="AA99" s="28" t="n"/>
       <c r="AB99" s="28" t="n"/>
       <c r="AC99" s="30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD99" s="24" t="inlineStr">
         <is>
@@ -29162,7 +29206,11 @@
       </c>
       <c r="AH99" s="24" t="n"/>
       <c r="AI99" s="31" t="n"/>
-      <c r="AJ99" s="31" t="n"/>
+      <c r="AJ99" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK99" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -29395,7 +29443,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="24" t="inlineStr">
         <is>
@@ -29423,7 +29471,7 @@
       <c r="AA100" s="28" t="n"/>
       <c r="AB100" s="28" t="n"/>
       <c r="AC100" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD100" s="24" t="inlineStr">
         <is>
@@ -29447,7 +29495,11 @@
       </c>
       <c r="AH100" s="24" t="n"/>
       <c r="AI100" s="31" t="n"/>
-      <c r="AJ100" s="31" t="n"/>
+      <c r="AJ100" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK100" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -29680,7 +29732,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101" s="24" t="inlineStr">
         <is>
@@ -29708,7 +29760,7 @@
       <c r="AA101" s="28" t="n"/>
       <c r="AB101" s="28" t="n"/>
       <c r="AC101" s="30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD101" s="24" t="inlineStr">
         <is>
@@ -29732,7 +29784,11 @@
       </c>
       <c r="AH101" s="24" t="n"/>
       <c r="AI101" s="31" t="n"/>
-      <c r="AJ101" s="31" t="n"/>
+      <c r="AJ101" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK101" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -29965,7 +30021,7 @@
         <v>10</v>
       </c>
       <c r="S102" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102" s="24" t="inlineStr">
         <is>
@@ -29993,7 +30049,7 @@
       <c r="AA102" s="28" t="n"/>
       <c r="AB102" s="28" t="n"/>
       <c r="AC102" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD102" s="24" t="inlineStr">
         <is>
@@ -30017,7 +30073,11 @@
       </c>
       <c r="AH102" s="24" t="n"/>
       <c r="AI102" s="31" t="n"/>
-      <c r="AJ102" s="31" t="n"/>
+      <c r="AJ102" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK102" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -30250,7 +30310,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" s="24" t="inlineStr">
         <is>
@@ -30278,7 +30338,7 @@
       <c r="AA103" s="28" t="n"/>
       <c r="AB103" s="28" t="n"/>
       <c r="AC103" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD103" s="24" t="inlineStr">
         <is>
@@ -30302,7 +30362,11 @@
       </c>
       <c r="AH103" s="24" t="n"/>
       <c r="AI103" s="31" t="n"/>
-      <c r="AJ103" s="31" t="n"/>
+      <c r="AJ103" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK103" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -30535,7 +30599,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" s="24" t="inlineStr">
         <is>
@@ -30563,7 +30627,7 @@
       <c r="AA104" s="28" t="n"/>
       <c r="AB104" s="28" t="n"/>
       <c r="AC104" s="30" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="AD104" s="24" t="inlineStr">
         <is>
@@ -30587,7 +30651,11 @@
       </c>
       <c r="AH104" s="24" t="n"/>
       <c r="AI104" s="31" t="n"/>
-      <c r="AJ104" s="31" t="n"/>
+      <c r="AJ104" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK104" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -30820,7 +30888,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="24" t="inlineStr">
         <is>
@@ -30848,7 +30916,7 @@
       <c r="AA105" s="28" t="n"/>
       <c r="AB105" s="28" t="n"/>
       <c r="AC105" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD105" s="24" t="inlineStr">
         <is>
@@ -30872,7 +30940,11 @@
       </c>
       <c r="AH105" s="24" t="n"/>
       <c r="AI105" s="31" t="n"/>
-      <c r="AJ105" s="31" t="n"/>
+      <c r="AJ105" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK105" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -31105,7 +31177,7 @@
         <v>38</v>
       </c>
       <c r="S106" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="24" t="inlineStr">
         <is>
@@ -31133,7 +31205,7 @@
       <c r="AA106" s="28" t="n"/>
       <c r="AB106" s="28" t="n"/>
       <c r="AC106" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD106" s="24" t="inlineStr">
         <is>
@@ -31157,7 +31229,11 @@
       </c>
       <c r="AH106" s="24" t="n"/>
       <c r="AI106" s="31" t="n"/>
-      <c r="AJ106" s="31" t="n"/>
+      <c r="AJ106" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK106" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -31390,7 +31466,7 @@
         <v>40</v>
       </c>
       <c r="S107" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" s="24" t="inlineStr">
         <is>
@@ -31428,7 +31504,11 @@
       </c>
       <c r="AH107" s="24" t="n"/>
       <c r="AI107" s="31" t="n"/>
-      <c r="AJ107" s="31" t="n"/>
+      <c r="AJ107" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK107" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -32217,7 +32297,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T110" s="24" t="inlineStr">
         <is>
@@ -32245,7 +32325,7 @@
       <c r="AA110" s="28" t="n"/>
       <c r="AB110" s="28" t="n"/>
       <c r="AC110" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD110" s="24" t="inlineStr">
         <is>
@@ -32269,7 +32349,11 @@
       </c>
       <c r="AH110" s="24" t="n"/>
       <c r="AI110" s="31" t="n"/>
-      <c r="AJ110" s="31" t="n"/>
+      <c r="AJ110" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK110" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -32502,7 +32586,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" s="24" t="inlineStr">
         <is>
@@ -32530,7 +32614,7 @@
       <c r="AA111" s="28" t="n"/>
       <c r="AB111" s="28" t="n"/>
       <c r="AC111" s="30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD111" s="24" t="inlineStr">
         <is>
@@ -32554,7 +32638,11 @@
       </c>
       <c r="AH111" s="24" t="n"/>
       <c r="AI111" s="31" t="n"/>
-      <c r="AJ111" s="31" t="n"/>
+      <c r="AJ111" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK111" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -33072,7 +33160,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="24" t="inlineStr">
         <is>
@@ -33100,7 +33188,7 @@
       <c r="AA113" s="28" t="n"/>
       <c r="AB113" s="28" t="n"/>
       <c r="AC113" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD113" s="24" t="inlineStr">
         <is>
@@ -33124,7 +33212,11 @@
       </c>
       <c r="AH113" s="24" t="n"/>
       <c r="AI113" s="31" t="n"/>
-      <c r="AJ113" s="31" t="n"/>
+      <c r="AJ113" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK113" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -33357,7 +33449,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T114" s="24" t="inlineStr">
         <is>
@@ -33385,7 +33477,7 @@
       <c r="AA114" s="28" t="n"/>
       <c r="AB114" s="28" t="n"/>
       <c r="AC114" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD114" s="24" t="inlineStr">
         <is>
@@ -33409,7 +33501,11 @@
       </c>
       <c r="AH114" s="24" t="n"/>
       <c r="AI114" s="31" t="n"/>
-      <c r="AJ114" s="31" t="n"/>
+      <c r="AJ114" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK114" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -33642,7 +33738,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" s="24" t="inlineStr">
         <is>
@@ -33670,7 +33766,7 @@
       <c r="AA115" s="28" t="n"/>
       <c r="AB115" s="28" t="n"/>
       <c r="AC115" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD115" s="24" t="inlineStr">
         <is>
@@ -33694,7 +33790,11 @@
       </c>
       <c r="AH115" s="24" t="n"/>
       <c r="AI115" s="31" t="n"/>
-      <c r="AJ115" s="31" t="n"/>
+      <c r="AJ115" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK115" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -33927,7 +34027,7 @@
         <v>0</v>
       </c>
       <c r="S116" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T116" s="24" t="inlineStr">
         <is>
@@ -33955,7 +34055,7 @@
       <c r="AA116" s="28" t="n"/>
       <c r="AB116" s="28" t="n"/>
       <c r="AC116" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD116" s="24" t="inlineStr">
         <is>
@@ -33979,7 +34079,11 @@
       </c>
       <c r="AH116" s="24" t="n"/>
       <c r="AI116" s="31" t="n"/>
-      <c r="AJ116" s="31" t="n"/>
+      <c r="AJ116" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK116" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -34212,7 +34316,7 @@
         <v>0</v>
       </c>
       <c r="S117" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" s="24" t="inlineStr">
         <is>
@@ -34240,7 +34344,7 @@
       <c r="AA117" s="28" t="n"/>
       <c r="AB117" s="28" t="n"/>
       <c r="AC117" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD117" s="24" t="inlineStr">
         <is>
@@ -34264,7 +34368,11 @@
       </c>
       <c r="AH117" s="24" t="n"/>
       <c r="AI117" s="31" t="n"/>
-      <c r="AJ117" s="31" t="n"/>
+      <c r="AJ117" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK117" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -34497,7 +34605,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" s="24" t="inlineStr">
         <is>
@@ -34525,7 +34633,7 @@
       <c r="AA118" s="28" t="n"/>
       <c r="AB118" s="28" t="n"/>
       <c r="AC118" s="30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD118" s="24" t="inlineStr">
         <is>
@@ -34549,7 +34657,11 @@
       </c>
       <c r="AH118" s="24" t="n"/>
       <c r="AI118" s="31" t="n"/>
-      <c r="AJ118" s="31" t="n"/>
+      <c r="AJ118" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK118" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -34782,7 +34894,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" s="24" t="inlineStr">
         <is>
@@ -34810,7 +34922,7 @@
       <c r="AA119" s="28" t="n"/>
       <c r="AB119" s="28" t="n"/>
       <c r="AC119" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD119" s="24" t="inlineStr">
         <is>
@@ -34834,7 +34946,11 @@
       </c>
       <c r="AH119" s="24" t="n"/>
       <c r="AI119" s="31" t="n"/>
-      <c r="AJ119" s="31" t="n"/>
+      <c r="AJ119" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK119" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -35067,7 +35183,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" s="24" t="inlineStr">
         <is>
@@ -35095,7 +35211,7 @@
       <c r="AA120" s="28" t="n"/>
       <c r="AB120" s="28" t="n"/>
       <c r="AC120" s="30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD120" s="24" t="inlineStr">
         <is>
@@ -35119,7 +35235,11 @@
       </c>
       <c r="AH120" s="24" t="n"/>
       <c r="AI120" s="31" t="n"/>
-      <c r="AJ120" s="31" t="n"/>
+      <c r="AJ120" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK120" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -35352,7 +35472,7 @@
         <v>0</v>
       </c>
       <c r="S121" s="29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T121" s="24" t="inlineStr">
         <is>
@@ -35380,7 +35500,7 @@
       <c r="AA121" s="28" t="n"/>
       <c r="AB121" s="28" t="n"/>
       <c r="AC121" s="30" t="n">
-        <v>0</v>
+        <v>1.9775</v>
       </c>
       <c r="AD121" s="24" t="inlineStr">
         <is>
@@ -35404,7 +35524,11 @@
       </c>
       <c r="AH121" s="24" t="n"/>
       <c r="AI121" s="31" t="n"/>
-      <c r="AJ121" s="31" t="n"/>
+      <c r="AJ121" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK121" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -39337,18 +39461,32 @@
       </c>
       <c r="U135" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V135" s="24" t="n"/>
-      <c r="W135" s="26" t="n"/>
-      <c r="X135" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V135" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W135" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X135" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y135" s="25" t="n"/>
       <c r="Z135" s="26" t="n"/>
       <c r="AA135" s="28" t="n"/>
       <c r="AB135" s="28" t="n"/>
-      <c r="AC135" s="30" t="n"/>
-      <c r="AD135" s="24" t="n"/>
+      <c r="AC135" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD135" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:14:07.780173Z</t>
+        </is>
+      </c>
       <c r="AE135" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.90 (home) / 1.33 (away) from EWMA attack/defense strengths. Executable ask 0.4500 (atc-clbf-efv-new-2026-08-12-new).</t>
@@ -39361,7 +39499,7 @@
       </c>
       <c r="AG135" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH135" s="24" t="n"/>
@@ -39528,7 +39666,7 @@
     <row r="136" ht="36" customHeight="1">
       <c r="A136" s="24" t="inlineStr">
         <is>
-          <t>ba31351503b5497e</t>
+          <t>843c5d8ab85c48ab</t>
         </is>
       </c>
       <c r="B136" s="24" t="inlineStr">
@@ -39538,12 +39676,12 @@
       </c>
       <c r="C136" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T22:00Z</t>
+          <t>2026-08-12T18:30Z</t>
         </is>
       </c>
       <c r="D136" s="24" t="inlineStr">
         <is>
-          <t>401902573</t>
+          <t>401886555</t>
         </is>
       </c>
       <c r="E136" s="24" t="inlineStr">
@@ -39553,78 +39691,90 @@
       </c>
       <c r="F136" s="24" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G136" s="24" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="H136" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I136" s="24" t="inlineStr">
         <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J136" s="25" t="n">
-        <v>2.5</v>
-      </c>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J136" s="25" t="n"/>
       <c r="K136" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L136" s="26" t="n">
-        <v>194</v>
+        <v>-186</v>
       </c>
       <c r="M136" s="27" t="n">
-        <v>2.94</v>
+        <v>1.537634</v>
       </c>
       <c r="N136" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.65035</v>
       </c>
       <c r="O136" s="28" t="n">
-        <v>0.550338</v>
+        <v>0.417429</v>
       </c>
       <c r="P136" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q136" s="28" t="n">
-        <v>0.210202</v>
+        <v>-0.232921</v>
       </c>
       <c r="R136" s="26" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="S136" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T136" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U136" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V136" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W136" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T136" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U136" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V136" s="24" t="n"/>
-      <c r="W136" s="26" t="n"/>
-      <c r="X136" s="26" t="n"/>
+      <c r="X136" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y136" s="25" t="n"/>
       <c r="Z136" s="26" t="n"/>
       <c r="AA136" s="28" t="n"/>
       <c r="AB136" s="28" t="n"/>
-      <c r="AC136" s="30" t="n"/>
-      <c r="AD136" s="24" t="n"/>
+      <c r="AC136" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD136" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:14:20.486952Z</t>
+        </is>
+      </c>
       <c r="AE136" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3400 (tsc-sud-tig-tor-2026-08-12-2pt5).</t>
+          <t>Poisson-DC rates 1.08 (home) / 0.75 (away) from EWMA attack/defense strengths. Executable ask 0.6500 (atc-clbf-afr-com-2026-08-12-afr).</t>
         </is>
       </c>
       <c r="AF136" s="31" t="inlineStr">
@@ -39634,7 +39784,7 @@
       </c>
       <c r="AG136" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH136" s="24" t="n"/>
@@ -39660,37 +39810,37 @@
       </c>
       <c r="AO136" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP136" s="24" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="AQ136" s="24" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="AR136" s="24" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="AS136" s="24" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AT136" s="24" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AU136" s="24" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="AV136" s="24" t="n"/>
@@ -39743,7 +39893,7 @@
       </c>
       <c r="BH136" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:31.711259Z</t>
+          <t>2026-08-12T17:41:32.473435Z</t>
         </is>
       </c>
       <c r="BI136" s="24" t="inlineStr">
@@ -39751,17 +39901,15 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ136" s="25" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="BJ136" s="25" t="n"/>
       <c r="BK136" s="26" t="n">
-        <v>194</v>
+        <v>-186</v>
       </c>
       <c r="BL136" s="27" t="n">
-        <v>2.94</v>
+        <v>1.537634</v>
       </c>
       <c r="BM136" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.65035</v>
       </c>
       <c r="BN136" s="28" t="n"/>
       <c r="BO136" s="28" t="n"/>
@@ -39796,14 +39944,14 @@
       <c r="CR136" s="24" t="n"/>
       <c r="CS136" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="137" ht="36" customHeight="1">
       <c r="A137" s="24" t="inlineStr">
         <is>
-          <t>b1f9c8be77ad4880</t>
+          <t>ce25c2f24a924c0f</t>
         </is>
       </c>
       <c r="B137" s="24" t="inlineStr">
@@ -39813,12 +39961,12 @@
       </c>
       <c r="C137" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T22:00Z</t>
+          <t>2026-08-12T18:30Z</t>
         </is>
       </c>
       <c r="D137" s="24" t="inlineStr">
         <is>
-          <t>401902573</t>
+          <t>401867394</t>
         </is>
       </c>
       <c r="E137" s="24" t="inlineStr">
@@ -39828,12 +39976,12 @@
       </c>
       <c r="F137" s="24" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G137" s="24" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="H137" s="24" t="inlineStr">
@@ -39862,16 +40010,16 @@
         <v>0.530516</v>
       </c>
       <c r="O137" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.5307269999999999</v>
       </c>
       <c r="P137" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q137" s="28" t="n">
-        <v>-0.074381</v>
+        <v>0.000211</v>
       </c>
       <c r="R137" s="26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S137" s="29" t="n">
         <v>1</v>
@@ -39883,21 +40031,35 @@
       </c>
       <c r="U137" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V137" s="24" t="n"/>
-      <c r="W137" s="26" t="n"/>
-      <c r="X137" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V137" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X137" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y137" s="25" t="n"/>
       <c r="Z137" s="26" t="n"/>
       <c r="AA137" s="28" t="n"/>
       <c r="AB137" s="28" t="n"/>
-      <c r="AC137" s="30" t="n"/>
-      <c r="AD137" s="24" t="n"/>
+      <c r="AC137" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD137" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:14:21.484779Z</t>
+        </is>
+      </c>
       <c r="AE137" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5300 (atc-sud-tig-tor-2026-08-12-tig).</t>
+          <t>Poisson-DC rates 1.71 (home) / 0.99 (away) from EWMA attack/defense strengths. Executable ask 0.5300 (atc-clbf-mun-lee-2026-08-12-mun).</t>
         </is>
       </c>
       <c r="AF137" s="31" t="inlineStr">
@@ -39907,7 +40069,7 @@
       </c>
       <c r="AG137" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH137" s="24" t="n"/>
@@ -39933,37 +40095,37 @@
       </c>
       <c r="AO137" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP137" s="24" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="AQ137" s="24" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="AR137" s="24" t="inlineStr">
         <is>
-          <t>Montevideo City Torque</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="AS137" s="24" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AT137" s="24" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AU137" s="24" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="AV137" s="24" t="n"/>
@@ -40016,7 +40178,7 @@
       </c>
       <c r="BH137" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:31.490640Z</t>
+          <t>2026-08-12T17:41:32.336635Z</t>
         </is>
       </c>
       <c r="BI137" s="24" t="inlineStr">
@@ -40067,14 +40229,14 @@
       <c r="CR137" s="24" t="n"/>
       <c r="CS137" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="138" ht="36" customHeight="1">
       <c r="A138" s="24" t="inlineStr">
         <is>
-          <t>843c5d8ab85c48ab</t>
+          <t>7441bf945d0c4b67</t>
         </is>
       </c>
       <c r="B138" s="24" t="inlineStr">
@@ -40084,12 +40246,12 @@
       </c>
       <c r="C138" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T18:30Z</t>
+          <t>2026-08-12T18:45Z</t>
         </is>
       </c>
       <c r="D138" s="24" t="inlineStr">
         <is>
-          <t>401886555</t>
+          <t>401906432</t>
         </is>
       </c>
       <c r="E138" s="24" t="inlineStr">
@@ -40099,12 +40261,12 @@
       </c>
       <c r="F138" s="24" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G138" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="H138" s="24" t="inlineStr">
@@ -40124,51 +40286,65 @@
         </is>
       </c>
       <c r="L138" s="26" t="n">
-        <v>-186</v>
+        <v>144</v>
       </c>
       <c r="M138" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.44</v>
       </c>
       <c r="N138" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.409836</v>
       </c>
       <c r="O138" s="28" t="n">
-        <v>0.417429</v>
+        <v>0.465639</v>
       </c>
       <c r="P138" s="28" t="n">
         <v>0.04</v>
       </c>
       <c r="Q138" s="28" t="n">
-        <v>-0.232921</v>
+        <v>0.055803</v>
       </c>
       <c r="R138" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="S138" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U138" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V138" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W138" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S138" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T138" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U138" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V138" s="24" t="n"/>
-      <c r="W138" s="26" t="n"/>
-      <c r="X138" s="26" t="n"/>
+      <c r="X138" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y138" s="25" t="n"/>
       <c r="Z138" s="26" t="n"/>
       <c r="AA138" s="28" t="n"/>
       <c r="AB138" s="28" t="n"/>
-      <c r="AC138" s="30" t="n"/>
-      <c r="AD138" s="24" t="n"/>
+      <c r="AC138" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD138" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:14:22.485912Z</t>
+        </is>
+      </c>
       <c r="AE138" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.08 (home) / 0.75 (away) from EWMA attack/defense strengths. Executable ask 0.6500 (atc-clbf-afr-com-2026-08-12-afr).</t>
+          <t>Poisson-DC rates 1.76 (home) / 1.33 (away) from EWMA attack/defense strengths. Executable ask 0.4100 (atc-clbf-nfo-lev-2026-08-12-nfo).</t>
         </is>
       </c>
       <c r="AF138" s="31" t="inlineStr">
@@ -40178,7 +40354,7 @@
       </c>
       <c r="AG138" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH138" s="24" t="n"/>
@@ -40209,32 +40385,32 @@
       </c>
       <c r="AP138" s="24" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="AQ138" s="24" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="AR138" s="24" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="AS138" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="AT138" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="AU138" s="24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="AV138" s="24" t="n"/>
@@ -40287,7 +40463,7 @@
       </c>
       <c r="BH138" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:32.473435Z</t>
+          <t>2026-08-12T17:41:32.663481Z</t>
         </is>
       </c>
       <c r="BI138" s="24" t="inlineStr">
@@ -40297,13 +40473,13 @@
       </c>
       <c r="BJ138" s="25" t="n"/>
       <c r="BK138" s="26" t="n">
-        <v>-186</v>
+        <v>144</v>
       </c>
       <c r="BL138" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.44</v>
       </c>
       <c r="BM138" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.409836</v>
       </c>
       <c r="BN138" s="28" t="n"/>
       <c r="BO138" s="28" t="n"/>
@@ -40338,14 +40514,14 @@
       <c r="CR138" s="24" t="n"/>
       <c r="CS138" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="139" ht="36" customHeight="1">
       <c r="A139" s="24" t="inlineStr">
         <is>
-          <t>ce25c2f24a924c0f</t>
+          <t>93356bd1ded542d7</t>
         </is>
       </c>
       <c r="B139" s="24" t="inlineStr">
@@ -40355,12 +40531,12 @@
       </c>
       <c r="C139" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T18:30Z</t>
+          <t>2026-08-12T19:00Z</t>
         </is>
       </c>
       <c r="D139" s="24" t="inlineStr">
         <is>
-          <t>401867394</t>
+          <t>401887955</t>
         </is>
       </c>
       <c r="E139" s="24" t="inlineStr">
@@ -40370,12 +40546,12 @@
       </c>
       <c r="F139" s="24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G139" s="24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="H139" s="24" t="inlineStr">
@@ -40385,7 +40561,7 @@
       </c>
       <c r="I139" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J139" s="25" t="n"/>
@@ -40395,25 +40571,25 @@
         </is>
       </c>
       <c r="L139" s="26" t="n">
-        <v>-113</v>
+        <v>-270</v>
       </c>
       <c r="M139" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.37037</v>
       </c>
       <c r="N139" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.72973</v>
       </c>
       <c r="O139" s="28" t="n">
-        <v>0.5307269999999999</v>
+        <v>0.444718</v>
       </c>
       <c r="P139" s="28" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="Q139" s="28" t="n">
-        <v>0.000211</v>
+        <v>-0.285012</v>
       </c>
       <c r="R139" s="26" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S139" s="29" t="n">
         <v>1</v>
@@ -40425,21 +40601,35 @@
       </c>
       <c r="U139" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V139" s="24" t="n"/>
-      <c r="W139" s="26" t="n"/>
-      <c r="X139" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V139" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W139" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X139" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y139" s="25" t="n"/>
       <c r="Z139" s="26" t="n"/>
       <c r="AA139" s="28" t="n"/>
       <c r="AB139" s="28" t="n"/>
-      <c r="AC139" s="30" t="n"/>
-      <c r="AD139" s="24" t="n"/>
+      <c r="AC139" s="30" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="AD139" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:14:23.558698Z</t>
+        </is>
+      </c>
       <c r="AE139" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.71 (home) / 0.99 (away) from EWMA attack/defense strengths. Executable ask 0.5300 (atc-clbf-mun-lee-2026-08-12-mun).</t>
+          <t>Poisson-DC rates 1.35 (home) / 1.69 (away) from EWMA attack/defense strengths. Executable ask 0.7300 (atc-clbf-dep-rme-2026-08-12-rme).</t>
         </is>
       </c>
       <c r="AF139" s="31" t="inlineStr">
@@ -40475,37 +40665,37 @@
       </c>
       <c r="AO139" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP139" s="24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="AQ139" s="24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="AR139" s="24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="AS139" s="24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="AT139" s="24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="AU139" s="24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="AV139" s="24" t="n"/>
@@ -40558,7 +40748,7 @@
       </c>
       <c r="BH139" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:32.336635Z</t>
+          <t>2026-08-12T17:41:32.802271Z</t>
         </is>
       </c>
       <c r="BI139" s="24" t="inlineStr">
@@ -40568,13 +40758,13 @@
       </c>
       <c r="BJ139" s="25" t="n"/>
       <c r="BK139" s="26" t="n">
-        <v>-113</v>
+        <v>-270</v>
       </c>
       <c r="BL139" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.37037</v>
       </c>
       <c r="BM139" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.72973</v>
       </c>
       <c r="BN139" s="28" t="n"/>
       <c r="BO139" s="28" t="n"/>
@@ -40609,14 +40799,14 @@
       <c r="CR139" s="24" t="n"/>
       <c r="CS139" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="140" ht="36" customHeight="1">
       <c r="A140" s="24" t="inlineStr">
         <is>
-          <t>7441bf945d0c4b67</t>
+          <t>1f6f7effab0b4f7e</t>
         </is>
       </c>
       <c r="B140" s="24" t="inlineStr">
@@ -40626,12 +40816,12 @@
       </c>
       <c r="C140" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T18:45Z</t>
+          <t>2026-08-12T19:00Z</t>
         </is>
       </c>
       <c r="D140" s="24" t="inlineStr">
         <is>
-          <t>401906432</t>
+          <t>401906428</t>
         </is>
       </c>
       <c r="E140" s="24" t="inlineStr">
@@ -40641,12 +40831,12 @@
       </c>
       <c r="F140" s="24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G140" s="24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="H140" s="24" t="inlineStr">
@@ -40666,25 +40856,25 @@
         </is>
       </c>
       <c r="L140" s="26" t="n">
-        <v>144</v>
+        <v>-257</v>
       </c>
       <c r="M140" s="27" t="n">
-        <v>2.44</v>
+        <v>1.389105</v>
       </c>
       <c r="N140" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.719888</v>
       </c>
       <c r="O140" s="28" t="n">
-        <v>0.465639</v>
+        <v>0.565923</v>
       </c>
       <c r="P140" s="28" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="Q140" s="28" t="n">
-        <v>0.055803</v>
+        <v>-0.153965</v>
       </c>
       <c r="R140" s="26" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="S140" s="29" t="n">
         <v>1</v>
@@ -40696,21 +40886,35 @@
       </c>
       <c r="U140" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V140" s="24" t="n"/>
-      <c r="W140" s="26" t="n"/>
-      <c r="X140" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V140" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W140" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X140" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y140" s="25" t="n"/>
       <c r="Z140" s="26" t="n"/>
       <c r="AA140" s="28" t="n"/>
       <c r="AB140" s="28" t="n"/>
-      <c r="AC140" s="30" t="n"/>
-      <c r="AD140" s="24" t="n"/>
+      <c r="AC140" s="30" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="AD140" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:15.478830Z</t>
+        </is>
+      </c>
       <c r="AE140" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.76 (home) / 1.33 (away) from EWMA attack/defense strengths. Executable ask 0.4100 (atc-clbf-nfo-lev-2026-08-12-nfo).</t>
+          <t>Poisson-DC rates 1.74 (home) / 0.88 (away) from EWMA attack/defense strengths. Executable ask 0.7200 (atc-clbf-nap-aris-2026-08-12-nap).</t>
         </is>
       </c>
       <c r="AF140" s="31" t="inlineStr">
@@ -40746,37 +40950,37 @@
       </c>
       <c r="AO140" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP140" s="24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="AQ140" s="24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="AR140" s="24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="AS140" s="24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="AT140" s="24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="AU140" s="24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="AV140" s="24" t="n"/>
@@ -40829,7 +41033,7 @@
       </c>
       <c r="BH140" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:32.663481Z</t>
+          <t>2026-08-12T17:41:32.874312Z</t>
         </is>
       </c>
       <c r="BI140" s="24" t="inlineStr">
@@ -40839,13 +41043,13 @@
       </c>
       <c r="BJ140" s="25" t="n"/>
       <c r="BK140" s="26" t="n">
-        <v>144</v>
+        <v>-257</v>
       </c>
       <c r="BL140" s="27" t="n">
-        <v>2.44</v>
+        <v>1.389105</v>
       </c>
       <c r="BM140" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.719888</v>
       </c>
       <c r="BN140" s="28" t="n"/>
       <c r="BO140" s="28" t="n"/>
@@ -40880,29 +41084,29 @@
       <c r="CR140" s="24" t="n"/>
       <c r="CS140" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="141" ht="36" customHeight="1">
       <c r="A141" s="24" t="inlineStr">
         <is>
-          <t>93356bd1ded542d7</t>
+          <t>297ea97baf454982</t>
         </is>
       </c>
       <c r="B141" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:43:17.410674Z</t>
+          <t>2026-08-12T21:32:30.006308Z</t>
         </is>
       </c>
       <c r="C141" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T19:00Z</t>
+          <t>2026-08-12T22:00Z</t>
         </is>
       </c>
       <c r="D141" s="24" t="inlineStr">
         <is>
-          <t>401887955</t>
+          <t>401902573</t>
         </is>
       </c>
       <c r="E141" s="24" t="inlineStr">
@@ -40912,50 +41116,52 @@
       </c>
       <c r="F141" s="24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="G141" s="24" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="H141" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I141" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J141" s="25" t="n"/>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J141" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K141" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L141" s="26" t="n">
-        <v>-270</v>
+        <v>203</v>
       </c>
       <c r="M141" s="27" t="n">
-        <v>1.37037</v>
+        <v>3.03</v>
       </c>
       <c r="N141" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.330033</v>
       </c>
       <c r="O141" s="28" t="n">
-        <v>0.444718</v>
+        <v>0.550338</v>
       </c>
       <c r="P141" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q141" s="28" t="n">
-        <v>-0.285012</v>
+        <v>0.220305</v>
       </c>
       <c r="R141" s="26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S141" s="29" t="n">
         <v>1</v>
@@ -40967,21 +41173,35 @@
       </c>
       <c r="U141" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V141" s="24" t="n"/>
-      <c r="W141" s="26" t="n"/>
-      <c r="X141" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V141" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W141" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X141" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y141" s="25" t="n"/>
       <c r="Z141" s="26" t="n"/>
       <c r="AA141" s="28" t="n"/>
       <c r="AB141" s="28" t="n"/>
-      <c r="AC141" s="30" t="n"/>
-      <c r="AD141" s="24" t="n"/>
+      <c r="AC141" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD141" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:45.267121Z</t>
+        </is>
+      </c>
       <c r="AE141" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.35 (home) / 1.69 (away) from EWMA attack/defense strengths. Executable ask 0.7300 (atc-clbf-dep-rme-2026-08-12-rme).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (tsc-sud-tig-tor-2026-08-12-2pt5).</t>
         </is>
       </c>
       <c r="AF141" s="31" t="inlineStr">
@@ -40991,7 +41211,7 @@
       </c>
       <c r="AG141" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH141" s="24" t="n"/>
@@ -41022,32 +41242,32 @@
       </c>
       <c r="AP141" s="24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="AQ141" s="24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="AR141" s="24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="AS141" s="24" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="AT141" s="24" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="AU141" s="24" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="AV141" s="24" t="n"/>
@@ -41100,7 +41320,7 @@
       </c>
       <c r="BH141" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:32.802271Z</t>
+          <t>2026-08-12T21:16:27.752629Z</t>
         </is>
       </c>
       <c r="BI141" s="24" t="inlineStr">
@@ -41108,15 +41328,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ141" s="25" t="n"/>
+      <c r="BJ141" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK141" s="26" t="n">
-        <v>-270</v>
+        <v>203</v>
       </c>
       <c r="BL141" s="27" t="n">
-        <v>1.37037</v>
+        <v>3.03</v>
       </c>
       <c r="BM141" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.330033</v>
       </c>
       <c r="BN141" s="28" t="n"/>
       <c r="BO141" s="28" t="n"/>
@@ -41151,29 +41373,29 @@
       <c r="CR141" s="24" t="n"/>
       <c r="CS141" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="24" t="inlineStr">
         <is>
-          <t>1f6f7effab0b4f7e</t>
+          <t>6f4d17d72452439a</t>
         </is>
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:43:17.410674Z</t>
+          <t>2026-08-12T21:32:30.006308Z</t>
         </is>
       </c>
       <c r="C142" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T19:00Z</t>
+          <t>2026-08-12T22:00Z</t>
         </is>
       </c>
       <c r="D142" s="24" t="inlineStr">
         <is>
-          <t>401906428</t>
+          <t>401902573</t>
         </is>
       </c>
       <c r="E142" s="24" t="inlineStr">
@@ -41183,12 +41405,12 @@
       </c>
       <c r="F142" s="24" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="G142" s="24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="H142" s="24" t="inlineStr">
@@ -41208,22 +41430,22 @@
         </is>
       </c>
       <c r="L142" s="26" t="n">
-        <v>-257</v>
+        <v>-108</v>
       </c>
       <c r="M142" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.925926</v>
       </c>
       <c r="N142" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.519231</v>
       </c>
       <c r="O142" s="28" t="n">
-        <v>0.565923</v>
+        <v>0.456135</v>
       </c>
       <c r="P142" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q142" s="28" t="n">
-        <v>-0.153965</v>
+        <v>-0.063096</v>
       </c>
       <c r="R142" s="26" t="n">
         <v>0</v>
@@ -41238,21 +41460,35 @@
       </c>
       <c r="U142" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V142" s="24" t="n"/>
-      <c r="W142" s="26" t="n"/>
-      <c r="X142" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V142" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W142" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y142" s="25" t="n"/>
       <c r="Z142" s="26" t="n"/>
       <c r="AA142" s="28" t="n"/>
       <c r="AB142" s="28" t="n"/>
-      <c r="AC142" s="30" t="n"/>
-      <c r="AD142" s="24" t="n"/>
+      <c r="AC142" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD142" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:46.272104Z</t>
+        </is>
+      </c>
       <c r="AE142" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.74 (home) / 0.88 (away) from EWMA attack/defense strengths. Executable ask 0.7200 (atc-clbf-nap-aris-2026-08-12-nap).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5200 (atc-sud-tig-tor-2026-08-12-tig).</t>
         </is>
       </c>
       <c r="AF142" s="31" t="inlineStr">
@@ -41262,7 +41498,7 @@
       </c>
       <c r="AG142" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH142" s="24" t="n"/>
@@ -41293,32 +41529,32 @@
       </c>
       <c r="AP142" s="24" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="AQ142" s="24" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="AR142" s="24" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Montevideo City Torque</t>
         </is>
       </c>
       <c r="AS142" s="24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="AT142" s="24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="AU142" s="24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="AV142" s="24" t="n"/>
@@ -41371,7 +41607,7 @@
       </c>
       <c r="BH142" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:32.874312Z</t>
+          <t>2026-08-12T21:16:27.579259Z</t>
         </is>
       </c>
       <c r="BI142" s="24" t="inlineStr">
@@ -41381,13 +41617,13 @@
       </c>
       <c r="BJ142" s="25" t="n"/>
       <c r="BK142" s="26" t="n">
-        <v>-257</v>
+        <v>-108</v>
       </c>
       <c r="BL142" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.925926</v>
       </c>
       <c r="BM142" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.519231</v>
       </c>
       <c r="BN142" s="28" t="n"/>
       <c r="BO142" s="28" t="n"/>
@@ -41426,6 +41662,1098 @@
         </is>
       </c>
     </row>
+    <row r="143" ht="36" customHeight="1">
+      <c r="A143" s="24" t="inlineStr">
+        <is>
+          <t>ca05d953249e4fb0</t>
+        </is>
+      </c>
+      <c r="B143" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:15:12.703088Z</t>
+        </is>
+      </c>
+      <c r="C143" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="D143" s="24" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="E143" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F143" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="G143" s="24" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="H143" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I143" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J143" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K143" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L143" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M143" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N143" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O143" s="28" t="n">
+        <v>0.550338</v>
+      </c>
+      <c r="P143" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q143" s="28" t="n">
+        <v>0.031107</v>
+      </c>
+      <c r="R143" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T143" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U143" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V143" s="24" t="n"/>
+      <c r="W143" s="26" t="n"/>
+      <c r="X143" s="26" t="n"/>
+      <c r="Y143" s="25" t="n"/>
+      <c r="Z143" s="26" t="n"/>
+      <c r="AA143" s="28" t="n"/>
+      <c r="AB143" s="28" t="n"/>
+      <c r="AC143" s="30" t="n"/>
+      <c r="AD143" s="24" t="n"/>
+      <c r="AE143" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5200 (tsc-sud-sfa-mac-2026-08-13-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF143" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG143" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH143" s="24" t="n"/>
+      <c r="AI143" s="31" t="n"/>
+      <c r="AJ143" s="31" t="n"/>
+      <c r="AK143" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL143" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM143" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN143" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO143" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP143" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="AQ143" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="AR143" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="AS143" s="24" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="AT143" s="24" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="AU143" s="24" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="AV143" s="24" t="n"/>
+      <c r="AW143" s="24" t="n"/>
+      <c r="AX143" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY143" s="24" t="n"/>
+      <c r="AZ143" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA143" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB143" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC143" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD143" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE143" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF143" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG143" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH143" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:47.780496Z</t>
+        </is>
+      </c>
+      <c r="BI143" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ143" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK143" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL143" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM143" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN143" s="28" t="n"/>
+      <c r="BO143" s="28" t="n"/>
+      <c r="BP143" s="25" t="n"/>
+      <c r="BQ143" s="27" t="n"/>
+      <c r="BR143" s="28" t="n"/>
+      <c r="BS143" s="28" t="n"/>
+      <c r="BT143" s="28" t="n"/>
+      <c r="BU143" s="25" t="n"/>
+      <c r="BV143" s="29" t="n"/>
+      <c r="BW143" s="24" t="n"/>
+      <c r="BX143" s="30" t="n"/>
+      <c r="BY143" s="27" t="n"/>
+      <c r="BZ143" s="24" t="n"/>
+      <c r="CA143" s="31" t="n"/>
+      <c r="CB143" s="24" t="n"/>
+      <c r="CC143" s="24" t="n"/>
+      <c r="CD143" s="24" t="n"/>
+      <c r="CE143" s="24" t="n"/>
+      <c r="CF143" s="24" t="n"/>
+      <c r="CG143" s="24" t="n"/>
+      <c r="CH143" s="24" t="n"/>
+      <c r="CI143" s="24" t="n"/>
+      <c r="CJ143" s="24" t="n"/>
+      <c r="CK143" s="24" t="n"/>
+      <c r="CL143" s="24" t="n"/>
+      <c r="CM143" s="24" t="n"/>
+      <c r="CN143" s="24" t="n"/>
+      <c r="CO143" s="24" t="n"/>
+      <c r="CP143" s="24" t="n"/>
+      <c r="CQ143" s="24" t="n"/>
+      <c r="CR143" s="24" t="n"/>
+      <c r="CS143" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="36" customHeight="1">
+      <c r="A144" s="24" t="inlineStr">
+        <is>
+          <t>4a2ff3d9275f4850</t>
+        </is>
+      </c>
+      <c r="B144" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:15:12.703088Z</t>
+        </is>
+      </c>
+      <c r="C144" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="D144" s="24" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="E144" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F144" s="24" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="G144" s="24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="H144" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I144" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J144" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K144" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L144" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M144" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N144" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O144" s="28" t="n">
+        <v>0.550338</v>
+      </c>
+      <c r="P144" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q144" s="28" t="n">
+        <v>0.159713</v>
+      </c>
+      <c r="R144" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="S144" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T144" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U144" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V144" s="24" t="n"/>
+      <c r="W144" s="26" t="n"/>
+      <c r="X144" s="26" t="n"/>
+      <c r="Y144" s="25" t="n"/>
+      <c r="Z144" s="26" t="n"/>
+      <c r="AA144" s="28" t="n"/>
+      <c r="AB144" s="28" t="n"/>
+      <c r="AC144" s="30" t="n"/>
+      <c r="AD144" s="24" t="n"/>
+      <c r="AE144" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (tsc-sud-vas-clo-2026-08-13-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF144" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG144" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH144" s="24" t="n"/>
+      <c r="AI144" s="31" t="n"/>
+      <c r="AJ144" s="31" t="n"/>
+      <c r="AK144" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL144" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM144" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN144" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO144" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP144" s="24" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="AQ144" s="24" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="AR144" s="24" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="AS144" s="24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="AT144" s="24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="AU144" s="24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="AV144" s="24" t="n"/>
+      <c r="AW144" s="24" t="n"/>
+      <c r="AX144" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY144" s="24" t="n"/>
+      <c r="AZ144" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA144" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB144" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC144" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD144" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE144" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF144" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG144" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH144" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:47.118202Z</t>
+        </is>
+      </c>
+      <c r="BI144" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ144" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK144" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL144" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM144" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN144" s="28" t="n"/>
+      <c r="BO144" s="28" t="n"/>
+      <c r="BP144" s="25" t="n"/>
+      <c r="BQ144" s="27" t="n"/>
+      <c r="BR144" s="28" t="n"/>
+      <c r="BS144" s="28" t="n"/>
+      <c r="BT144" s="28" t="n"/>
+      <c r="BU144" s="25" t="n"/>
+      <c r="BV144" s="29" t="n"/>
+      <c r="BW144" s="24" t="n"/>
+      <c r="BX144" s="30" t="n"/>
+      <c r="BY144" s="27" t="n"/>
+      <c r="BZ144" s="24" t="n"/>
+      <c r="CA144" s="31" t="n"/>
+      <c r="CB144" s="24" t="n"/>
+      <c r="CC144" s="24" t="n"/>
+      <c r="CD144" s="24" t="n"/>
+      <c r="CE144" s="24" t="n"/>
+      <c r="CF144" s="24" t="n"/>
+      <c r="CG144" s="24" t="n"/>
+      <c r="CH144" s="24" t="n"/>
+      <c r="CI144" s="24" t="n"/>
+      <c r="CJ144" s="24" t="n"/>
+      <c r="CK144" s="24" t="n"/>
+      <c r="CL144" s="24" t="n"/>
+      <c r="CM144" s="24" t="n"/>
+      <c r="CN144" s="24" t="n"/>
+      <c r="CO144" s="24" t="n"/>
+      <c r="CP144" s="24" t="n"/>
+      <c r="CQ144" s="24" t="n"/>
+      <c r="CR144" s="24" t="n"/>
+      <c r="CS144" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="36" customHeight="1">
+      <c r="A145" s="24" t="inlineStr">
+        <is>
+          <t>521ba8dc0554415b</t>
+        </is>
+      </c>
+      <c r="B145" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:15:12.703088Z</t>
+        </is>
+      </c>
+      <c r="C145" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="D145" s="24" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="E145" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F145" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="G145" s="24" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="H145" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I145" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J145" s="25" t="n"/>
+      <c r="K145" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L145" s="26" t="n">
+        <v>-245</v>
+      </c>
+      <c r="M145" s="27" t="n">
+        <v>1.408163</v>
+      </c>
+      <c r="N145" s="28" t="n">
+        <v>0.710145</v>
+      </c>
+      <c r="O145" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P145" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q145" s="28" t="n">
+        <v>-0.25401</v>
+      </c>
+      <c r="R145" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T145" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U145" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V145" s="24" t="n"/>
+      <c r="W145" s="26" t="n"/>
+      <c r="X145" s="26" t="n"/>
+      <c r="Y145" s="25" t="n"/>
+      <c r="Z145" s="26" t="n"/>
+      <c r="AA145" s="28" t="n"/>
+      <c r="AB145" s="28" t="n"/>
+      <c r="AC145" s="30" t="n"/>
+      <c r="AD145" s="24" t="n"/>
+      <c r="AE145" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.7100 (atc-sud-sfa-mac-2026-08-13-sfa).</t>
+        </is>
+      </c>
+      <c r="AF145" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG145" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH145" s="24" t="n"/>
+      <c r="AI145" s="31" t="n"/>
+      <c r="AJ145" s="31" t="n"/>
+      <c r="AK145" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM145" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN145" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO145" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP145" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="AQ145" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="AR145" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="AS145" s="24" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="AT145" s="24" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="AU145" s="24" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="AV145" s="24" t="n"/>
+      <c r="AW145" s="24" t="n"/>
+      <c r="AX145" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY145" s="24" t="n"/>
+      <c r="AZ145" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA145" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB145" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC145" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD145" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE145" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF145" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG145" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH145" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:47.664302Z</t>
+        </is>
+      </c>
+      <c r="BI145" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ145" s="25" t="n"/>
+      <c r="BK145" s="26" t="n">
+        <v>-245</v>
+      </c>
+      <c r="BL145" s="27" t="n">
+        <v>1.408163</v>
+      </c>
+      <c r="BM145" s="28" t="n">
+        <v>0.710145</v>
+      </c>
+      <c r="BN145" s="28" t="n"/>
+      <c r="BO145" s="28" t="n"/>
+      <c r="BP145" s="25" t="n"/>
+      <c r="BQ145" s="27" t="n"/>
+      <c r="BR145" s="28" t="n"/>
+      <c r="BS145" s="28" t="n"/>
+      <c r="BT145" s="28" t="n"/>
+      <c r="BU145" s="25" t="n"/>
+      <c r="BV145" s="29" t="n"/>
+      <c r="BW145" s="24" t="n"/>
+      <c r="BX145" s="30" t="n"/>
+      <c r="BY145" s="27" t="n"/>
+      <c r="BZ145" s="24" t="n"/>
+      <c r="CA145" s="31" t="n"/>
+      <c r="CB145" s="24" t="n"/>
+      <c r="CC145" s="24" t="n"/>
+      <c r="CD145" s="24" t="n"/>
+      <c r="CE145" s="24" t="n"/>
+      <c r="CF145" s="24" t="n"/>
+      <c r="CG145" s="24" t="n"/>
+      <c r="CH145" s="24" t="n"/>
+      <c r="CI145" s="24" t="n"/>
+      <c r="CJ145" s="24" t="n"/>
+      <c r="CK145" s="24" t="n"/>
+      <c r="CL145" s="24" t="n"/>
+      <c r="CM145" s="24" t="n"/>
+      <c r="CN145" s="24" t="n"/>
+      <c r="CO145" s="24" t="n"/>
+      <c r="CP145" s="24" t="n"/>
+      <c r="CQ145" s="24" t="n"/>
+      <c r="CR145" s="24" t="n"/>
+      <c r="CS145" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="36" customHeight="1">
+      <c r="A146" s="24" t="inlineStr">
+        <is>
+          <t>e47243ef18d1450c</t>
+        </is>
+      </c>
+      <c r="B146" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:15:12.703088Z</t>
+        </is>
+      </c>
+      <c r="C146" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="D146" s="24" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="E146" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F146" s="24" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="G146" s="24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="H146" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I146" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J146" s="25" t="n"/>
+      <c r="K146" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L146" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M146" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N146" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O146" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P146" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q146" s="28" t="n">
+        <v>-0.093415</v>
+      </c>
+      <c r="R146" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T146" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U146" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V146" s="24" t="n"/>
+      <c r="W146" s="26" t="n"/>
+      <c r="X146" s="26" t="n"/>
+      <c r="Y146" s="25" t="n"/>
+      <c r="Z146" s="26" t="n"/>
+      <c r="AA146" s="28" t="n"/>
+      <c r="AB146" s="28" t="n"/>
+      <c r="AC146" s="30" t="n"/>
+      <c r="AD146" s="24" t="n"/>
+      <c r="AE146" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5500 (atc-sud-vas-clo-2026-08-13-vas).</t>
+        </is>
+      </c>
+      <c r="AF146" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG146" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH146" s="24" t="n"/>
+      <c r="AI146" s="31" t="n"/>
+      <c r="AJ146" s="31" t="n"/>
+      <c r="AK146" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL146" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM146" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN146" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO146" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP146" s="24" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="AQ146" s="24" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="AR146" s="24" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="AS146" s="24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="AT146" s="24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="AU146" s="24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="AV146" s="24" t="n"/>
+      <c r="AW146" s="24" t="n"/>
+      <c r="AX146" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY146" s="24" t="n"/>
+      <c r="AZ146" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA146" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BB146" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC146" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD146" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BE146" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF146" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG146" s="24" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="BH146" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:47.108429Z</t>
+        </is>
+      </c>
+      <c r="BI146" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ146" s="25" t="n"/>
+      <c r="BK146" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL146" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM146" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN146" s="28" t="n"/>
+      <c r="BO146" s="28" t="n"/>
+      <c r="BP146" s="25" t="n"/>
+      <c r="BQ146" s="27" t="n"/>
+      <c r="BR146" s="28" t="n"/>
+      <c r="BS146" s="28" t="n"/>
+      <c r="BT146" s="28" t="n"/>
+      <c r="BU146" s="25" t="n"/>
+      <c r="BV146" s="29" t="n"/>
+      <c r="BW146" s="24" t="n"/>
+      <c r="BX146" s="30" t="n"/>
+      <c r="BY146" s="27" t="n"/>
+      <c r="BZ146" s="24" t="n"/>
+      <c r="CA146" s="31" t="n"/>
+      <c r="CB146" s="24" t="n"/>
+      <c r="CC146" s="24" t="n"/>
+      <c r="CD146" s="24" t="n"/>
+      <c r="CE146" s="24" t="n"/>
+      <c r="CF146" s="24" t="n"/>
+      <c r="CG146" s="24" t="n"/>
+      <c r="CH146" s="24" t="n"/>
+      <c r="CI146" s="24" t="n"/>
+      <c r="CJ146" s="24" t="n"/>
+      <c r="CK146" s="24" t="n"/>
+      <c r="CL146" s="24" t="n"/>
+      <c r="CM146" s="24" t="n"/>
+      <c r="CN146" s="24" t="n"/>
+      <c r="CO146" s="24" t="n"/>
+      <c r="CP146" s="24" t="n"/>
+      <c r="CQ146" s="24" t="n"/>
+      <c r="CR146" s="24" t="n"/>
+      <c r="CS146" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
